--- a/data/fmsForecastOutput/File1/RPT_RPT9537148419924KB_fmsForecastOutput.xlsx
+++ b/data/fmsForecastOutput/File1/RPT_RPT9537148419924KB_fmsForecastOutput.xlsx
@@ -1875,49 +1875,49 @@
         </is>
       </c>
       <c r="C8" s="148" t="n">
-        <v>216.1334652283321</v>
+        <v>216.1334652283319</v>
       </c>
       <c r="D8" s="149" t="n">
-        <v>243.9667551291313</v>
+        <v>243.9667551291312</v>
       </c>
       <c r="E8" s="149" t="n">
-        <v>275.4001197158068</v>
+        <v>275.4001197158066</v>
       </c>
       <c r="F8" s="149" t="n">
-        <v>298.5089243363709</v>
+        <v>298.5089243363707</v>
       </c>
       <c r="G8" s="150" t="n">
-        <v>317.6553552581552</v>
+        <v>317.655355258155</v>
       </c>
       <c r="H8" s="148" t="n">
-        <v>39.813395607265</v>
+        <v>39.81339560726497</v>
       </c>
       <c r="I8" s="149" t="n">
         <v>43.23244220626533</v>
       </c>
       <c r="J8" s="149" t="n">
-        <v>47.89461068103476</v>
+        <v>47.89461068103473</v>
       </c>
       <c r="K8" s="149" t="n">
-        <v>54.07187906873418</v>
+        <v>54.07187906873415</v>
       </c>
       <c r="L8" s="150" t="n">
-        <v>58.82705711554032</v>
+        <v>58.82705711554028</v>
       </c>
       <c r="M8" s="151" t="n">
-        <v>11775245.61338573</v>
+        <v>11775245.61338572</v>
       </c>
       <c r="N8" s="152" t="n">
         <v>12951571.06665268</v>
       </c>
       <c r="O8" s="152" t="n">
-        <v>14529409.26621108</v>
+        <v>14529409.26621107</v>
       </c>
       <c r="P8" s="152" t="n">
-        <v>16617237.82976372</v>
+        <v>16617237.82976371</v>
       </c>
       <c r="Q8" s="153" t="n">
-        <v>18393072.45273898</v>
+        <v>18393072.45273897</v>
       </c>
       <c r="S8" s="21" t="inlineStr">
         <is>
@@ -1925,49 +1925,49 @@
         </is>
       </c>
       <c r="T8" s="148" t="n">
-        <v>265.8694983145931</v>
+        <v>265.8694983145929</v>
       </c>
       <c r="U8" s="149" t="n">
-        <v>300.1077076291592</v>
+        <v>300.1077076291591</v>
       </c>
       <c r="V8" s="149" t="n">
-        <v>338.7744308234145</v>
+        <v>338.7744308234142</v>
       </c>
       <c r="W8" s="149" t="n">
-        <v>367.2009694190393</v>
+        <v>367.200969419039</v>
       </c>
       <c r="X8" s="150" t="n">
-        <v>390.7533238788729</v>
+        <v>390.7533238788727</v>
       </c>
       <c r="Y8" s="148" t="n">
-        <v>49.39925786435098</v>
+        <v>49.39925786435094</v>
       </c>
       <c r="Z8" s="149" t="n">
-        <v>53.64549440228228</v>
+        <v>53.64549440228226</v>
       </c>
       <c r="AA8" s="149" t="n">
-        <v>59.43268232428613</v>
+        <v>59.43268232428609</v>
       </c>
       <c r="AB8" s="149" t="n">
-        <v>67.09293788255478</v>
+        <v>67.09293788255474</v>
       </c>
       <c r="AC8" s="150" t="n">
-        <v>72.99007194932521</v>
+        <v>72.99007194932517</v>
       </c>
       <c r="AD8" s="151" t="n">
-        <v>11775245.61338573</v>
+        <v>11775245.61338572</v>
       </c>
       <c r="AE8" s="152" t="n">
         <v>12951571.06665268</v>
       </c>
       <c r="AF8" s="152" t="n">
-        <v>14529409.26621108</v>
+        <v>14529409.26621107</v>
       </c>
       <c r="AG8" s="152" t="n">
-        <v>16617237.82976372</v>
+        <v>16617237.82976371</v>
       </c>
       <c r="AH8" s="153" t="n">
-        <v>18393072.45273898</v>
+        <v>18393072.45273897</v>
       </c>
       <c r="AQ8" s="28" t="inlineStr">
         <is>
@@ -2025,13 +2025,13 @@
         <v>295.6338757286618</v>
       </c>
       <c r="D9" s="156" t="n">
-        <v>329.532726025456</v>
+        <v>329.5327260254559</v>
       </c>
       <c r="E9" s="156" t="n">
-        <v>401.2860412850875</v>
+        <v>401.2860412850877</v>
       </c>
       <c r="F9" s="156" t="n">
-        <v>431.9307316239914</v>
+        <v>431.9307316239913</v>
       </c>
       <c r="G9" s="157" t="n">
         <v>448.0049619414277</v>
@@ -2052,16 +2052,16 @@
         <v>29.58163533805693</v>
       </c>
       <c r="M9" s="158" t="n">
-        <v>6593767.945674589</v>
+        <v>6593767.945674586</v>
       </c>
       <c r="N9" s="159" t="n">
-        <v>5995429.771478218</v>
+        <v>5995429.771478217</v>
       </c>
       <c r="O9" s="159" t="n">
         <v>6580069.091165543</v>
       </c>
       <c r="P9" s="159" t="n">
-        <v>7474270.121441578</v>
+        <v>7474270.121441576</v>
       </c>
       <c r="Q9" s="160" t="n">
         <v>8285795.383143711</v>
@@ -2072,16 +2072,16 @@
         </is>
       </c>
       <c r="T9" s="155" t="n">
-        <v>351.6771583083325</v>
+        <v>351.6771583083324</v>
       </c>
       <c r="U9" s="156" t="n">
-        <v>392.0022100735026</v>
+        <v>392.0022100735025</v>
       </c>
       <c r="V9" s="156" t="n">
-        <v>477.3577937241034</v>
+        <v>477.3577937241035</v>
       </c>
       <c r="W9" s="156" t="n">
-        <v>513.8117947720614</v>
+        <v>513.8117947720613</v>
       </c>
       <c r="X9" s="157" t="n">
         <v>532.9332152320698</v>
@@ -2102,16 +2102,16 @@
         <v>30.87254372319671</v>
       </c>
       <c r="AD9" s="158" t="n">
-        <v>6593767.945674589</v>
+        <v>6593767.945674586</v>
       </c>
       <c r="AE9" s="159" t="n">
-        <v>5995429.771478218</v>
+        <v>5995429.771478217</v>
       </c>
       <c r="AF9" s="159" t="n">
         <v>6580069.091165543</v>
       </c>
       <c r="AG9" s="159" t="n">
-        <v>7474270.121441578</v>
+        <v>7474270.121441576</v>
       </c>
       <c r="AH9" s="160" t="n">
         <v>8285795.383143711</v>
@@ -2170,46 +2170,46 @@
         </is>
       </c>
       <c r="C10" s="161" t="n">
-        <v>239.2259865129068</v>
+        <v>239.2259865129066</v>
       </c>
       <c r="D10" s="162" t="n">
         <v>265.8065226600866</v>
       </c>
       <c r="E10" s="162" t="n">
-        <v>305.2491728116328</v>
+        <v>305.2491728116327</v>
       </c>
       <c r="F10" s="162" t="n">
-        <v>330.1481935878891</v>
+        <v>330.148193587889</v>
       </c>
       <c r="G10" s="163" t="n">
-        <v>349.2113647928792</v>
+        <v>349.2113647928791</v>
       </c>
       <c r="H10" s="161" t="n">
-        <v>32.39223937934148</v>
+        <v>32.39223937934146</v>
       </c>
       <c r="I10" s="162" t="n">
-        <v>33.06158192789842</v>
+        <v>33.06158192789841</v>
       </c>
       <c r="J10" s="162" t="n">
-        <v>36.45964040531643</v>
+        <v>36.45964040531642</v>
       </c>
       <c r="K10" s="162" t="n">
-        <v>41.19276042549244</v>
+        <v>41.19276042549242</v>
       </c>
       <c r="L10" s="163" t="n">
-        <v>45.00766351011701</v>
+        <v>45.00766351011699</v>
       </c>
       <c r="M10" s="164" t="n">
-        <v>18369013.55906032</v>
+        <v>18369013.55906031</v>
       </c>
       <c r="N10" s="165" t="n">
         <v>18947000.8381309</v>
       </c>
       <c r="O10" s="165" t="n">
-        <v>21109478.35737662</v>
+        <v>21109478.35737661</v>
       </c>
       <c r="P10" s="165" t="n">
-        <v>24091507.9512053</v>
+        <v>24091507.95120528</v>
       </c>
       <c r="Q10" s="166" t="n">
         <v>26678867.83588269</v>
@@ -2220,46 +2220,46 @@
         </is>
       </c>
       <c r="T10" s="161" t="n">
-        <v>291.390976214291</v>
+        <v>291.3909762142908</v>
       </c>
       <c r="U10" s="162" t="n">
         <v>324.1530504819149</v>
       </c>
       <c r="V10" s="162" t="n">
-        <v>372.4818196483732</v>
+        <v>372.4818196483731</v>
       </c>
       <c r="W10" s="162" t="n">
-        <v>402.8646296146745</v>
+        <v>402.8646296146743</v>
       </c>
       <c r="X10" s="163" t="n">
-        <v>426.0552249633645</v>
+        <v>426.0552249633644</v>
       </c>
       <c r="Y10" s="161" t="n">
-        <v>36.90103134339892</v>
+        <v>36.9010313433989</v>
       </c>
       <c r="Z10" s="162" t="n">
-        <v>37.6322404785754</v>
+        <v>37.63224047857539</v>
       </c>
       <c r="AA10" s="162" t="n">
-        <v>41.4895481920368</v>
+        <v>41.48954819203679</v>
       </c>
       <c r="AB10" s="162" t="n">
-        <v>46.89533929218953</v>
+        <v>46.89533929218951</v>
       </c>
       <c r="AC10" s="163" t="n">
-        <v>51.26791576644972</v>
+        <v>51.2679157664497</v>
       </c>
       <c r="AD10" s="164" t="n">
-        <v>18369013.55906032</v>
+        <v>18369013.55906031</v>
       </c>
       <c r="AE10" s="165" t="n">
         <v>18947000.8381309</v>
       </c>
       <c r="AF10" s="165" t="n">
-        <v>21109478.35737662</v>
+        <v>21109478.35737661</v>
       </c>
       <c r="AG10" s="165" t="n">
-        <v>24091507.9512053</v>
+        <v>24091507.95120528</v>
       </c>
       <c r="AH10" s="166" t="n">
         <v>26678867.83588269</v>
@@ -2324,13 +2324,13 @@
         <v>596.1576232056381</v>
       </c>
       <c r="E11" s="156" t="n">
-        <v>687.2962497855178</v>
+        <v>687.2962497855179</v>
       </c>
       <c r="F11" s="156" t="n">
-        <v>748.5003910405843</v>
+        <v>748.5003910405844</v>
       </c>
       <c r="G11" s="157" t="n">
-        <v>799.1742007978376</v>
+        <v>799.1742007978379</v>
       </c>
       <c r="H11" s="155" t="n">
         <v>44.46416719064507</v>
@@ -2339,13 +2339,13 @@
         <v>43.88282709914375</v>
       </c>
       <c r="J11" s="156" t="n">
-        <v>48.46110315186457</v>
+        <v>48.46110315186458</v>
       </c>
       <c r="K11" s="156" t="n">
         <v>56.85229339720815</v>
       </c>
       <c r="L11" s="157" t="n">
-        <v>66.31259056053378</v>
+        <v>66.31259056053381</v>
       </c>
       <c r="M11" s="158" t="n">
         <v>189293.2600794438</v>
@@ -2360,7 +2360,7 @@
         <v>249352.822709384</v>
       </c>
       <c r="Q11" s="160" t="n">
-        <v>294486.2326762782</v>
+        <v>294486.2326762783</v>
       </c>
       <c r="S11" s="32" t="inlineStr">
         <is>
@@ -2374,13 +2374,13 @@
         <v>609.7270386741711</v>
       </c>
       <c r="V11" s="156" t="n">
-        <v>702.940113086562</v>
+        <v>702.9401130865621</v>
       </c>
       <c r="W11" s="156" t="n">
-        <v>765.5373497056012</v>
+        <v>765.5373497056013</v>
       </c>
       <c r="X11" s="157" t="n">
-        <v>817.3645691505006</v>
+        <v>817.364569150501</v>
       </c>
       <c r="Y11" s="155" t="n">
         <v>45.15533454004876</v>
@@ -2389,13 +2389,13 @@
         <v>44.56099455422801</v>
       </c>
       <c r="AA11" s="156" t="n">
-        <v>49.20884712638486</v>
+        <v>49.20884712638487</v>
       </c>
       <c r="AB11" s="156" t="n">
         <v>57.73193599439708</v>
       </c>
       <c r="AC11" s="157" t="n">
-        <v>67.34225370357915</v>
+        <v>67.34225370357916</v>
       </c>
       <c r="AD11" s="158" t="n">
         <v>189293.2600794438</v>
@@ -2410,7 +2410,7 @@
         <v>249352.822709384</v>
       </c>
       <c r="AH11" s="160" t="n">
-        <v>294486.2326762782</v>
+        <v>294486.2326762783</v>
       </c>
       <c r="AJ11" s="39" t="n"/>
       <c r="AQ11" s="40" t="inlineStr">
@@ -2461,49 +2461,49 @@
         </is>
       </c>
       <c r="C12" s="161" t="n">
-        <v>240.5556849507623</v>
+        <v>240.5556849507621</v>
       </c>
       <c r="D12" s="162" t="n">
         <v>267.2672358731453</v>
       </c>
       <c r="E12" s="162" t="n">
-        <v>306.9337740175904</v>
+        <v>306.9337740175903</v>
       </c>
       <c r="F12" s="162" t="n">
-        <v>332.0494079649319</v>
+        <v>332.0494079649318</v>
       </c>
       <c r="G12" s="163" t="n">
-        <v>351.3712539359112</v>
+        <v>351.3712539359111</v>
       </c>
       <c r="H12" s="161" t="n">
-        <v>32.48219091504742</v>
+        <v>32.48219091504739</v>
       </c>
       <c r="I12" s="162" t="n">
-        <v>33.14218811819336</v>
+        <v>33.14218811819335</v>
       </c>
       <c r="J12" s="162" t="n">
-        <v>36.54901128631239</v>
+        <v>36.54901128631238</v>
       </c>
       <c r="K12" s="162" t="n">
-        <v>41.30932249399223</v>
+        <v>41.30932249399221</v>
       </c>
       <c r="L12" s="163" t="n">
-        <v>45.16608955912069</v>
+        <v>45.16608955912068</v>
       </c>
       <c r="M12" s="164" t="n">
-        <v>18558306.81913976</v>
+        <v>18558306.81913975</v>
       </c>
       <c r="N12" s="165" t="n">
-        <v>19135734.65352813</v>
+        <v>19135734.65352812</v>
       </c>
       <c r="O12" s="165" t="n">
-        <v>21319985.29902064</v>
+        <v>21319985.29902063</v>
       </c>
       <c r="P12" s="165" t="n">
-        <v>24340860.77391468</v>
+        <v>24340860.77391467</v>
       </c>
       <c r="Q12" s="166" t="n">
-        <v>26973354.06855897</v>
+        <v>26973354.06855896</v>
       </c>
       <c r="S12" s="42" t="inlineStr">
         <is>
@@ -2511,49 +2511,49 @@
         </is>
       </c>
       <c r="T12" s="161" t="n">
-        <v>292.7479908271904</v>
+        <v>292.7479908271903</v>
       </c>
       <c r="U12" s="162" t="n">
-        <v>325.657399901275</v>
+        <v>325.6573999012749</v>
       </c>
       <c r="V12" s="162" t="n">
-        <v>374.218834337951</v>
+        <v>374.2188343379509</v>
       </c>
       <c r="W12" s="162" t="n">
-        <v>404.8293413707548</v>
+        <v>404.8293413707546</v>
       </c>
       <c r="X12" s="163" t="n">
-        <v>428.2938237558374</v>
+        <v>428.2938237558373</v>
       </c>
       <c r="Y12" s="161" t="n">
-        <v>36.96996275410195</v>
+        <v>36.96996275410193</v>
       </c>
       <c r="Z12" s="162" t="n">
-        <v>37.69004096065451</v>
+        <v>37.6900409606545</v>
       </c>
       <c r="AA12" s="162" t="n">
-        <v>41.55390968080607</v>
+        <v>41.55390968080606</v>
       </c>
       <c r="AB12" s="162" t="n">
-        <v>46.98568774798557</v>
+        <v>46.98568774798554</v>
       </c>
       <c r="AC12" s="163" t="n">
-        <v>51.40186937097266</v>
+        <v>51.40186937097265</v>
       </c>
       <c r="AD12" s="164" t="n">
-        <v>18558306.81913976</v>
+        <v>18558306.81913975</v>
       </c>
       <c r="AE12" s="165" t="n">
-        <v>19135734.65352813</v>
+        <v>19135734.65352812</v>
       </c>
       <c r="AF12" s="165" t="n">
-        <v>21319985.29902064</v>
+        <v>21319985.29902063</v>
       </c>
       <c r="AG12" s="165" t="n">
-        <v>24340860.77391468</v>
+        <v>24340860.77391467</v>
       </c>
       <c r="AH12" s="166" t="n">
-        <v>26973354.06855897</v>
+        <v>26973354.06855896</v>
       </c>
       <c r="AQ12" s="40" t="inlineStr">
         <is>
@@ -2603,49 +2603,49 @@
         </is>
       </c>
       <c r="C13" s="155" t="n">
-        <v>947.8591485462172</v>
+        <v>947.8591485462168</v>
       </c>
       <c r="D13" s="156" t="n">
-        <v>966.8146387551301</v>
+        <v>966.8146387551297</v>
       </c>
       <c r="E13" s="156" t="n">
-        <v>846.9588199382875</v>
+        <v>846.9588199382872</v>
       </c>
       <c r="F13" s="156" t="n">
-        <v>874.9131918259558</v>
+        <v>874.9131918259552</v>
       </c>
       <c r="G13" s="157" t="n">
-        <v>912.1028898581559</v>
+        <v>912.1028898581555</v>
       </c>
       <c r="H13" s="155" t="n">
-        <v>829.3350195536839</v>
+        <v>829.3350195536837</v>
       </c>
       <c r="I13" s="156" t="n">
-        <v>851.119248541606</v>
+        <v>851.1192485416055</v>
       </c>
       <c r="J13" s="156" t="n">
-        <v>746.2435640328197</v>
+        <v>746.2435640328194</v>
       </c>
       <c r="K13" s="156" t="n">
-        <v>776.1142954230251</v>
+        <v>776.1142954230245</v>
       </c>
       <c r="L13" s="157" t="n">
-        <v>816.4013968752948</v>
+        <v>816.4013968752945</v>
       </c>
       <c r="M13" s="158" t="n">
-        <v>7641214.656498311</v>
+        <v>7641214.656498308</v>
       </c>
       <c r="N13" s="159" t="n">
-        <v>8787875.696365627</v>
+        <v>8787875.696365623</v>
       </c>
       <c r="O13" s="159" t="n">
-        <v>8681680.728870433</v>
+        <v>8681680.728870429</v>
       </c>
       <c r="P13" s="159" t="n">
-        <v>10162681.59710787</v>
+        <v>10162681.59710786</v>
       </c>
       <c r="Q13" s="160" t="n">
-        <v>12084613.03805428</v>
+        <v>12084613.03805427</v>
       </c>
       <c r="S13" s="32" t="inlineStr">
         <is>
@@ -2653,49 +2653,49 @@
         </is>
       </c>
       <c r="T13" s="155" t="n">
-        <v>618.5905654383046</v>
+        <v>618.5905654383045</v>
       </c>
       <c r="U13" s="156" t="n">
-        <v>630.9612720189984</v>
+        <v>630.9612720189982</v>
       </c>
       <c r="V13" s="156" t="n">
-        <v>552.7411283967137</v>
+        <v>552.7411283967135</v>
       </c>
       <c r="W13" s="156" t="n">
-        <v>570.9846730615383</v>
+        <v>570.9846730615378</v>
       </c>
       <c r="X13" s="157" t="n">
-        <v>595.2553638804249</v>
+        <v>595.2553638804246</v>
       </c>
       <c r="Y13" s="155" t="n">
-        <v>543.7347312224258</v>
+        <v>543.7347312224257</v>
       </c>
       <c r="Z13" s="156" t="n">
-        <v>557.9064574414627</v>
+        <v>557.9064574414625</v>
       </c>
       <c r="AA13" s="156" t="n">
-        <v>489.1471491792705</v>
+        <v>489.1471491792703</v>
       </c>
       <c r="AB13" s="156" t="n">
-        <v>508.614498639201</v>
+        <v>508.6144986392006</v>
       </c>
       <c r="AC13" s="157" t="n">
-        <v>534.858337625937</v>
+        <v>534.8583376259368</v>
       </c>
       <c r="AD13" s="158" t="n">
-        <v>7641214.656498311</v>
+        <v>7641214.656498308</v>
       </c>
       <c r="AE13" s="159" t="n">
-        <v>8787875.696365627</v>
+        <v>8787875.696365623</v>
       </c>
       <c r="AF13" s="159" t="n">
-        <v>8681680.728870433</v>
+        <v>8681680.728870429</v>
       </c>
       <c r="AG13" s="159" t="n">
-        <v>10162681.59710787</v>
+        <v>10162681.59710786</v>
       </c>
       <c r="AH13" s="160" t="n">
-        <v>12084613.03805428</v>
+        <v>12084613.03805427</v>
       </c>
       <c r="AJ13" s="39" t="n"/>
       <c r="AQ13" s="49" t="inlineStr">
@@ -2746,49 +2746,49 @@
         </is>
       </c>
       <c r="C14" s="167" t="n">
-        <v>307.472901030977</v>
+        <v>307.4729010309769</v>
       </c>
       <c r="D14" s="168" t="n">
         <v>346.0720602558285</v>
       </c>
       <c r="E14" s="168" t="n">
-        <v>376.3776341688291</v>
+        <v>376.3776341688289</v>
       </c>
       <c r="F14" s="168" t="n">
-        <v>406.3036485831515</v>
+        <v>406.3036485831513</v>
       </c>
       <c r="G14" s="169" t="n">
-        <v>433.9043987089516</v>
+        <v>433.9043987089515</v>
       </c>
       <c r="H14" s="167" t="n">
-        <v>45.12867240894707</v>
+        <v>45.12867240894703</v>
       </c>
       <c r="I14" s="168" t="n">
-        <v>47.51272469690296</v>
+        <v>47.51272469690295</v>
       </c>
       <c r="J14" s="168" t="n">
-        <v>50.4263789544683</v>
+        <v>50.42637895446828</v>
       </c>
       <c r="K14" s="168" t="n">
-        <v>57.28360595425106</v>
+        <v>57.28360595425102</v>
       </c>
       <c r="L14" s="169" t="n">
-        <v>63.81958668865224</v>
+        <v>63.81958668865222</v>
       </c>
       <c r="M14" s="170" t="n">
-        <v>26199521.47563808</v>
+        <v>26199521.47563806</v>
       </c>
       <c r="N14" s="171" t="n">
         <v>27923610.34989375</v>
       </c>
       <c r="O14" s="171" t="n">
-        <v>30001666.02789108</v>
+        <v>30001666.02789106</v>
       </c>
       <c r="P14" s="171" t="n">
-        <v>34503542.37102255</v>
+        <v>34503542.37102253</v>
       </c>
       <c r="Q14" s="172" t="n">
-        <v>39057967.10661324</v>
+        <v>39057967.10661323</v>
       </c>
       <c r="S14" s="51" t="inlineStr">
         <is>
@@ -2796,49 +2796,49 @@
         </is>
       </c>
       <c r="T14" s="167" t="n">
-        <v>345.8861853350951</v>
+        <v>345.8861853350948</v>
       </c>
       <c r="U14" s="168" t="n">
-        <v>384.1566502760281</v>
+        <v>384.156650276028</v>
       </c>
       <c r="V14" s="168" t="n">
-        <v>412.799359127015</v>
+        <v>412.7993591270149</v>
       </c>
       <c r="W14" s="168" t="n">
-        <v>442.7803004622236</v>
+        <v>442.7803004622234</v>
       </c>
       <c r="X14" s="169" t="n">
-        <v>468.9947424244635</v>
+        <v>468.9947424244634</v>
       </c>
       <c r="Y14" s="167" t="n">
-        <v>50.77066701841002</v>
+        <v>50.77066701840999</v>
       </c>
       <c r="Z14" s="168" t="n">
-        <v>53.34381563760422</v>
+        <v>53.3438156376042</v>
       </c>
       <c r="AA14" s="168" t="n">
-        <v>56.51982287673964</v>
+        <v>56.51982287673961</v>
       </c>
       <c r="AB14" s="168" t="n">
-        <v>64.12945990411419</v>
+        <v>64.12945990411414</v>
       </c>
       <c r="AC14" s="169" t="n">
-        <v>71.35851346967662</v>
+        <v>71.35851346967659</v>
       </c>
       <c r="AD14" s="170" t="n">
-        <v>26199521.47563808</v>
+        <v>26199521.47563806</v>
       </c>
       <c r="AE14" s="171" t="n">
         <v>27923610.34989375</v>
       </c>
       <c r="AF14" s="171" t="n">
-        <v>30001666.02789108</v>
+        <v>30001666.02789106</v>
       </c>
       <c r="AG14" s="171" t="n">
-        <v>34503542.37102255</v>
+        <v>34503542.37102253</v>
       </c>
       <c r="AH14" s="172" t="n">
-        <v>39057967.10661324</v>
+        <v>39057967.10661323</v>
       </c>
       <c r="AR14" s="58" t="inlineStr">
         <is>
@@ -3155,7 +3155,7 @@
         <v>54481.36224969088</v>
       </c>
       <c r="D19" s="75" t="n">
-        <v>53087.44242549536</v>
+        <v>53087.44242549535</v>
       </c>
       <c r="E19" s="75" t="n">
         <v>52757.45443104524</v>
@@ -3345,7 +3345,7 @@
         <v>15294.37747392813</v>
       </c>
       <c r="V20" s="80" t="n">
-        <v>13784.35458198175</v>
+        <v>13784.35458198174</v>
       </c>
       <c r="W20" s="80" t="n">
         <v>14546.70795316665</v>
@@ -3412,7 +3412,7 @@
         <v>76785.19305873683</v>
       </c>
       <c r="D21" s="86" t="n">
-        <v>71281.17342086569</v>
+        <v>71281.17342086567</v>
       </c>
       <c r="E21" s="86" t="n">
         <v>69154.90765442021</v>
@@ -3625,7 +3625,7 @@
         <v>299.4663951096735</v>
       </c>
       <c r="W22" s="80" t="n">
-        <v>325.7226088384536</v>
+        <v>325.7226088384535</v>
       </c>
       <c r="X22" s="81" t="n">
         <v>360.2874944559221</v>
@@ -3706,7 +3706,7 @@
         <v>77147.65428610983</v>
       </c>
       <c r="D23" s="86" t="n">
-        <v>71597.75716994597</v>
+        <v>71597.75716994595</v>
       </c>
       <c r="E23" s="86" t="n">
         <v>69461.19034068499</v>
@@ -3945,7 +3945,7 @@
         <v>85209.20506421653</v>
       </c>
       <c r="D25" s="92" t="n">
-        <v>80687.27168917263</v>
+        <v>80687.2716891726</v>
       </c>
       <c r="E25" s="92" t="n">
         <v>79711.60691879326</v>
@@ -3998,7 +3998,7 @@
         <v>72688.08266062764</v>
       </c>
       <c r="V25" s="92" t="n">
-        <v>72678.56735857918</v>
+        <v>72678.56735857917</v>
       </c>
       <c r="W25" s="92" t="n">
         <v>77924.74582767999</v>
@@ -4408,34 +4408,34 @@
         </is>
       </c>
       <c r="C35" s="148" t="n">
-        <v>221.0360737948077</v>
+        <v>221.0360737948075</v>
       </c>
       <c r="D35" s="149" t="n">
-        <v>256.0373391449633</v>
+        <v>256.0373391449632</v>
       </c>
       <c r="E35" s="149" t="n">
-        <v>290.7627916682948</v>
+        <v>290.7627916682947</v>
       </c>
       <c r="F35" s="149" t="n">
-        <v>319.9911447958211</v>
+        <v>319.9911447958209</v>
       </c>
       <c r="G35" s="150" t="n">
-        <v>341.4154535024092</v>
+        <v>341.415453502409</v>
       </c>
       <c r="H35" s="148" t="n">
-        <v>40.71649265500101</v>
+        <v>40.71649265500098</v>
       </c>
       <c r="I35" s="149" t="n">
-        <v>45.37142555087766</v>
+        <v>45.37142555087765</v>
       </c>
       <c r="J35" s="149" t="n">
-        <v>50.56632045713852</v>
+        <v>50.56632045713849</v>
       </c>
       <c r="K35" s="149" t="n">
-        <v>57.9631665047586</v>
+        <v>57.96316650475856</v>
       </c>
       <c r="L35" s="150" t="n">
-        <v>63.22722425690539</v>
+        <v>63.22722425690535</v>
       </c>
       <c r="M35" s="151" t="n">
         <v>12042346.40666432</v>
@@ -4444,13 +4444,13 @@
         <v>13592367.50063526</v>
       </c>
       <c r="O35" s="152" t="n">
-        <v>15339904.73168357</v>
+        <v>15339904.73168356</v>
       </c>
       <c r="P35" s="152" t="n">
-        <v>17813098.78192691</v>
+        <v>17813098.7819269</v>
       </c>
       <c r="Q35" s="153" t="n">
-        <v>19768844.02799103</v>
+        <v>19768844.02799102</v>
       </c>
       <c r="S35" s="21" t="inlineStr">
         <is>
@@ -4458,34 +4458,34 @@
         </is>
       </c>
       <c r="T35" s="148" t="n">
-        <v>271.9002815559791</v>
+        <v>271.9002815559789</v>
       </c>
       <c r="U35" s="149" t="n">
-        <v>314.9559409338122</v>
+        <v>314.9559409338121</v>
       </c>
       <c r="V35" s="149" t="n">
-        <v>357.6723182026996</v>
+        <v>357.6723182026994</v>
       </c>
       <c r="W35" s="149" t="n">
-        <v>393.6266188213829</v>
+        <v>393.6266188213826</v>
       </c>
       <c r="X35" s="150" t="n">
-        <v>419.9810299790442</v>
+        <v>419.9810299790439</v>
       </c>
       <c r="Y35" s="148" t="n">
-        <v>50.51979338404688</v>
+        <v>50.51979338404684</v>
       </c>
       <c r="Z35" s="149" t="n">
-        <v>56.2996775384676</v>
+        <v>56.29967753846758</v>
       </c>
       <c r="AA35" s="149" t="n">
-        <v>62.74802148516463</v>
+        <v>62.74802148516459</v>
       </c>
       <c r="AB35" s="149" t="n">
-        <v>71.92128693801259</v>
+        <v>71.92128693801254</v>
       </c>
       <c r="AC35" s="150" t="n">
-        <v>78.44960931163956</v>
+        <v>78.44960931163952</v>
       </c>
       <c r="AD35" s="151" t="n">
         <v>12042346.40666432</v>
@@ -4494,13 +4494,13 @@
         <v>13592367.50063526</v>
       </c>
       <c r="AF35" s="152" t="n">
-        <v>15339904.73168357</v>
+        <v>15339904.73168356</v>
       </c>
       <c r="AG35" s="152" t="n">
-        <v>17813098.78192691</v>
+        <v>17813098.7819269</v>
       </c>
       <c r="AH35" s="153" t="n">
-        <v>19768844.02799103</v>
+        <v>19768844.02799102</v>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1" thickBot="1">
@@ -4510,25 +4510,25 @@
         </is>
       </c>
       <c r="C36" s="155" t="n">
-        <v>300.077895273195</v>
+        <v>300.0778952731949</v>
       </c>
       <c r="D36" s="156" t="n">
-        <v>344.5819267028969</v>
+        <v>344.5819267028968</v>
       </c>
       <c r="E36" s="156" t="n">
-        <v>421.7096072478324</v>
+        <v>421.7096072478325</v>
       </c>
       <c r="F36" s="156" t="n">
-        <v>463.216589047668</v>
+        <v>463.2165890476679</v>
       </c>
       <c r="G36" s="157" t="n">
         <v>481.627164733281</v>
       </c>
       <c r="H36" s="155" t="n">
-        <v>24.667889004872</v>
+        <v>24.66788900487199</v>
       </c>
       <c r="I36" s="156" t="n">
-        <v>22.92204977440284</v>
+        <v>22.92204977440283</v>
       </c>
       <c r="J36" s="156" t="n">
         <v>25.08875953058551</v>
@@ -4540,16 +4540,16 @@
         <v>31.8016994595361</v>
       </c>
       <c r="M36" s="158" t="n">
-        <v>6692886.60570795</v>
+        <v>6692886.605707948</v>
       </c>
       <c r="N36" s="159" t="n">
-        <v>6269230.880298922</v>
+        <v>6269230.880298921</v>
       </c>
       <c r="O36" s="159" t="n">
         <v>6914963.558694163</v>
       </c>
       <c r="P36" s="159" t="n">
-        <v>8015650.792565092</v>
+        <v>8015650.792565091</v>
       </c>
       <c r="Q36" s="160" t="n">
         <v>8907633.791934108</v>
@@ -4560,22 +4560,22 @@
         </is>
       </c>
       <c r="T36" s="155" t="n">
-        <v>356.9636301682845</v>
+        <v>356.9636301682843</v>
       </c>
       <c r="U36" s="156" t="n">
-        <v>409.9042861329855</v>
+        <v>409.9042861329854</v>
       </c>
       <c r="V36" s="156" t="n">
-        <v>501.6530529280693</v>
+        <v>501.6530529280694</v>
       </c>
       <c r="W36" s="156" t="n">
-        <v>551.0285088812948</v>
+        <v>551.0285088812947</v>
       </c>
       <c r="X36" s="157" t="n">
         <v>572.9291754540232</v>
       </c>
       <c r="Y36" s="155" t="n">
-        <v>25.7991799176683</v>
+        <v>25.79917991766829</v>
       </c>
       <c r="Z36" s="156" t="n">
         <v>23.9238864215984</v>
@@ -4584,22 +4584,22 @@
         <v>26.16114234717341</v>
       </c>
       <c r="AB36" s="156" t="n">
-        <v>30.12787051881011</v>
+        <v>30.1278705188101</v>
       </c>
       <c r="AC36" s="157" t="n">
         <v>33.18948887769566</v>
       </c>
       <c r="AD36" s="158" t="n">
-        <v>6692886.60570795</v>
+        <v>6692886.605707948</v>
       </c>
       <c r="AE36" s="159" t="n">
-        <v>6269230.880298922</v>
+        <v>6269230.880298921</v>
       </c>
       <c r="AF36" s="159" t="n">
         <v>6914963.558694163</v>
       </c>
       <c r="AG36" s="159" t="n">
-        <v>8015650.792565092</v>
+        <v>8015650.792565091</v>
       </c>
       <c r="AH36" s="160" t="n">
         <v>8907633.791934108</v>
@@ -4612,49 +4612,49 @@
         </is>
       </c>
       <c r="C37" s="161" t="n">
-        <v>243.99538851248</v>
+        <v>243.9953885124798</v>
       </c>
       <c r="D37" s="162" t="n">
         <v>278.6373656290039</v>
       </c>
       <c r="E37" s="162" t="n">
-        <v>321.8118430811794</v>
+        <v>321.8118430811793</v>
       </c>
       <c r="F37" s="162" t="n">
-        <v>353.955220732701</v>
+        <v>353.9552207327009</v>
       </c>
       <c r="G37" s="163" t="n">
-        <v>375.3589552057339</v>
+        <v>375.3589552057338</v>
       </c>
       <c r="H37" s="161" t="n">
-        <v>33.03803716042054</v>
+        <v>33.03803716042052</v>
       </c>
       <c r="I37" s="162" t="n">
-        <v>34.65750952882992</v>
+        <v>34.65750952882991</v>
       </c>
       <c r="J37" s="162" t="n">
-        <v>38.43792259562441</v>
+        <v>38.4379225956244</v>
       </c>
       <c r="K37" s="162" t="n">
-        <v>44.16317548353626</v>
+        <v>44.16317548353624</v>
       </c>
       <c r="L37" s="163" t="n">
-        <v>48.3776625122976</v>
+        <v>48.37766251229758</v>
       </c>
       <c r="M37" s="164" t="n">
-        <v>18735233.01237227</v>
+        <v>18735233.01237226</v>
       </c>
       <c r="N37" s="165" t="n">
-        <v>19861598.38093419</v>
+        <v>19861598.38093418</v>
       </c>
       <c r="O37" s="165" t="n">
-        <v>22254868.29037773</v>
+        <v>22254868.29037772</v>
       </c>
       <c r="P37" s="165" t="n">
-        <v>25828749.574492</v>
+        <v>25828749.57449199</v>
       </c>
       <c r="Q37" s="166" t="n">
-        <v>28676477.81992514</v>
+        <v>28676477.81992513</v>
       </c>
       <c r="S37" s="42" t="inlineStr">
         <is>
@@ -4662,49 +4662,49 @@
         </is>
       </c>
       <c r="T37" s="161" t="n">
-        <v>297.2003814752828</v>
+        <v>297.2003814752826</v>
       </c>
       <c r="U37" s="162" t="n">
-        <v>339.8003598368765</v>
+        <v>339.8003598368764</v>
       </c>
       <c r="V37" s="162" t="n">
-        <v>392.6925003306882</v>
+        <v>392.6925003306881</v>
       </c>
       <c r="W37" s="162" t="n">
-        <v>431.9152479709064</v>
+        <v>431.9152479709062</v>
       </c>
       <c r="X37" s="163" t="n">
-        <v>457.9565851101231</v>
+        <v>457.9565851101229</v>
       </c>
       <c r="Y37" s="161" t="n">
-        <v>37.63672003358236</v>
+        <v>37.63672003358234</v>
       </c>
       <c r="Z37" s="162" t="n">
-        <v>39.44879999456067</v>
+        <v>39.44879999456066</v>
       </c>
       <c r="AA37" s="162" t="n">
-        <v>43.740750709664</v>
+        <v>43.74075070966398</v>
       </c>
       <c r="AB37" s="162" t="n">
-        <v>50.27696801885744</v>
+        <v>50.27696801885741</v>
       </c>
       <c r="AC37" s="163" t="n">
-        <v>55.10665813835662</v>
+        <v>55.10665813835661</v>
       </c>
       <c r="AD37" s="164" t="n">
-        <v>18735233.01237227</v>
+        <v>18735233.01237226</v>
       </c>
       <c r="AE37" s="165" t="n">
-        <v>19861598.38093419</v>
+        <v>19861598.38093418</v>
       </c>
       <c r="AF37" s="165" t="n">
-        <v>22254868.29037773</v>
+        <v>22254868.29037772</v>
       </c>
       <c r="AG37" s="165" t="n">
-        <v>25828749.574492</v>
+        <v>25828749.57449199</v>
       </c>
       <c r="AH37" s="166" t="n">
-        <v>28676477.81992514</v>
+        <v>28676477.81992513</v>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1" thickBot="1">
@@ -4720,13 +4720,13 @@
         <v>625.4325753706868</v>
       </c>
       <c r="E38" s="156" t="n">
-        <v>725.1255397186708</v>
+        <v>725.1255397186709</v>
       </c>
       <c r="F38" s="156" t="n">
-        <v>800.636208180984</v>
+        <v>800.6362081809841</v>
       </c>
       <c r="G38" s="157" t="n">
-        <v>856.8565791084674</v>
+        <v>856.8565791084677</v>
       </c>
       <c r="H38" s="155" t="n">
         <v>45.26361484619594</v>
@@ -4741,7 +4741,7 @@
         <v>60.8122656404404</v>
       </c>
       <c r="L38" s="157" t="n">
-        <v>71.09886610803261</v>
+        <v>71.09886610803264</v>
       </c>
       <c r="M38" s="158" t="n">
         <v>192696.6759656167</v>
@@ -4750,13 +4750,13 @@
         <v>198001.7895077849</v>
       </c>
       <c r="O38" s="159" t="n">
-        <v>222093.3981842343</v>
+        <v>222093.3981842344</v>
       </c>
       <c r="P38" s="159" t="n">
         <v>266721.1679017569</v>
       </c>
       <c r="Q38" s="160" t="n">
-        <v>315741.5062618706</v>
+        <v>315741.5062618707</v>
       </c>
       <c r="S38" s="32" t="inlineStr">
         <is>
@@ -4770,13 +4770,13 @@
         <v>639.6683313728072</v>
       </c>
       <c r="V38" s="156" t="n">
-        <v>741.63045273543</v>
+        <v>741.6304527354301</v>
       </c>
       <c r="W38" s="156" t="n">
-        <v>818.8598539502696</v>
+        <v>818.8598539502697</v>
       </c>
       <c r="X38" s="157" t="n">
-        <v>876.359882373044</v>
+        <v>876.3598823730443</v>
       </c>
       <c r="Y38" s="155" t="n">
         <v>45.96720910364684</v>
@@ -4785,13 +4785,13 @@
         <v>46.74920943771368</v>
       </c>
       <c r="AA38" s="156" t="n">
-        <v>51.91733818217214</v>
+        <v>51.91733818217215</v>
       </c>
       <c r="AB38" s="156" t="n">
         <v>61.75317859385747</v>
       </c>
       <c r="AC38" s="157" t="n">
-        <v>72.20284773995105</v>
+        <v>72.20284773995107</v>
       </c>
       <c r="AD38" s="158" t="n">
         <v>192696.6759656167</v>
@@ -4800,13 +4800,13 @@
         <v>198001.7895077849</v>
       </c>
       <c r="AF38" s="159" t="n">
-        <v>222093.3981842343</v>
+        <v>222093.3981842344</v>
       </c>
       <c r="AG38" s="159" t="n">
         <v>266721.1679017569</v>
       </c>
       <c r="AH38" s="160" t="n">
-        <v>315741.5062618706</v>
+        <v>315741.5062618707</v>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1" thickTop="1">
@@ -4816,37 +4816,37 @@
         </is>
       </c>
       <c r="C39" s="161" t="n">
-        <v>245.3467945783778</v>
+        <v>245.3467945783776</v>
       </c>
       <c r="D39" s="162" t="n">
         <v>280.1707897473391</v>
       </c>
       <c r="E39" s="162" t="n">
-        <v>323.5902174771212</v>
+        <v>323.5902174771211</v>
       </c>
       <c r="F39" s="162" t="n">
-        <v>355.9851761636974</v>
+        <v>355.9851761636972</v>
       </c>
       <c r="G39" s="163" t="n">
-        <v>377.6702160634012</v>
+        <v>377.6702160634011</v>
       </c>
       <c r="H39" s="161" t="n">
-        <v>33.12913358718165</v>
+        <v>33.12913358718163</v>
       </c>
       <c r="I39" s="162" t="n">
-        <v>34.74227953416757</v>
+        <v>34.74227953416756</v>
       </c>
       <c r="J39" s="162" t="n">
-        <v>38.53242462015204</v>
+        <v>38.53242462015203</v>
       </c>
       <c r="K39" s="162" t="n">
-        <v>44.28710334210225</v>
+        <v>44.28710334210223</v>
       </c>
       <c r="L39" s="163" t="n">
-        <v>48.54662016729272</v>
+        <v>48.54662016729271</v>
       </c>
       <c r="M39" s="164" t="n">
-        <v>18927929.68833789</v>
+        <v>18927929.68833788</v>
       </c>
       <c r="N39" s="165" t="n">
         <v>20059600.17044197</v>
@@ -4855,10 +4855,10 @@
         <v>22476961.68856196</v>
       </c>
       <c r="P39" s="165" t="n">
-        <v>26095470.74239376</v>
+        <v>26095470.74239374</v>
       </c>
       <c r="Q39" s="166" t="n">
-        <v>28992219.32618701</v>
+        <v>28992219.326187</v>
       </c>
       <c r="S39" s="42" t="inlineStr">
         <is>
@@ -4866,37 +4866,37 @@
         </is>
       </c>
       <c r="T39" s="161" t="n">
-        <v>298.5786063772005</v>
+        <v>298.5786063772003</v>
       </c>
       <c r="U39" s="162" t="n">
         <v>341.3800072400603</v>
       </c>
       <c r="V39" s="162" t="n">
-        <v>394.5266511482455</v>
+        <v>394.5266511482454</v>
       </c>
       <c r="W39" s="162" t="n">
-        <v>434.0114481376268</v>
+        <v>434.0114481376266</v>
       </c>
       <c r="X39" s="163" t="n">
-        <v>460.3501827329071</v>
+        <v>460.3501827329069</v>
       </c>
       <c r="Y39" s="161" t="n">
-        <v>37.70628766997337</v>
+        <v>37.70628766997335</v>
       </c>
       <c r="Z39" s="162" t="n">
-        <v>39.50970086946282</v>
+        <v>39.50970086946281</v>
       </c>
       <c r="AA39" s="162" t="n">
-        <v>43.80892495026002</v>
+        <v>43.80892495026001</v>
       </c>
       <c r="AB39" s="162" t="n">
-        <v>50.37264915679534</v>
+        <v>50.37264915679531</v>
       </c>
       <c r="AC39" s="163" t="n">
-        <v>55.2491272235344</v>
+        <v>55.24912722353439</v>
       </c>
       <c r="AD39" s="164" t="n">
-        <v>18927929.68833789</v>
+        <v>18927929.68833788</v>
       </c>
       <c r="AE39" s="165" t="n">
         <v>20059600.17044197</v>
@@ -4905,10 +4905,10 @@
         <v>22476961.68856196</v>
       </c>
       <c r="AG39" s="165" t="n">
-        <v>26095470.74239376</v>
+        <v>26095470.74239374</v>
       </c>
       <c r="AH39" s="166" t="n">
-        <v>28992219.32618701</v>
+        <v>28992219.326187</v>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1" thickBot="1">
@@ -4918,46 +4918,46 @@
         </is>
       </c>
       <c r="C40" s="155" t="n">
-        <v>921.4658679731419</v>
+        <v>921.4658679731417</v>
       </c>
       <c r="D40" s="156" t="n">
-        <v>951.5996717218443</v>
+        <v>951.5996717218438</v>
       </c>
       <c r="E40" s="156" t="n">
-        <v>879.1789239242275</v>
+        <v>879.1789239242272</v>
       </c>
       <c r="F40" s="156" t="n">
-        <v>918.7940300041741</v>
+        <v>918.7940300041735</v>
       </c>
       <c r="G40" s="157" t="n">
-        <v>959.480865608966</v>
+        <v>959.4808656089657</v>
       </c>
       <c r="H40" s="155" t="n">
-        <v>806.2420611814094</v>
+        <v>806.2420611814092</v>
       </c>
       <c r="I40" s="156" t="n">
-        <v>837.7250044033194</v>
+        <v>837.7250044033191</v>
       </c>
       <c r="J40" s="156" t="n">
-        <v>774.6322467715247</v>
+        <v>774.6322467715245</v>
       </c>
       <c r="K40" s="156" t="n">
-        <v>815.0399238435809</v>
+        <v>815.0399238435804</v>
       </c>
       <c r="L40" s="157" t="n">
-        <v>858.8082854118506</v>
+        <v>858.8082854118503</v>
       </c>
       <c r="M40" s="158" t="n">
-        <v>7428443.884957647</v>
+        <v>7428443.884957645</v>
       </c>
       <c r="N40" s="159" t="n">
-        <v>8649579.032607021</v>
+        <v>8649579.032607017</v>
       </c>
       <c r="O40" s="159" t="n">
-        <v>9011950.216916285</v>
+        <v>9011950.216916282</v>
       </c>
       <c r="P40" s="159" t="n">
-        <v>10672385.86352629</v>
+        <v>10672385.86352628</v>
       </c>
       <c r="Q40" s="160" t="n">
         <v>12712332.24587731</v>
@@ -4968,46 +4968,46 @@
         </is>
       </c>
       <c r="T40" s="155" t="n">
-        <v>601.3658180921282</v>
+        <v>601.3658180921281</v>
       </c>
       <c r="U40" s="156" t="n">
-        <v>621.0317006531675</v>
+        <v>621.0317006531673</v>
       </c>
       <c r="V40" s="156" t="n">
-        <v>573.7685694186346</v>
+        <v>573.7685694186343</v>
       </c>
       <c r="W40" s="156" t="n">
-        <v>599.6221267825932</v>
+        <v>599.6221267825928</v>
       </c>
       <c r="X40" s="157" t="n">
-        <v>626.1751148307286</v>
+        <v>626.1751148307284</v>
       </c>
       <c r="Y40" s="155" t="n">
-        <v>528.5943558401868</v>
+        <v>528.5943558401867</v>
       </c>
       <c r="Z40" s="156" t="n">
-        <v>549.1265651877015</v>
+        <v>549.1265651877013</v>
       </c>
       <c r="AA40" s="156" t="n">
-        <v>507.7553407937467</v>
+        <v>507.7553407937465</v>
       </c>
       <c r="AB40" s="156" t="n">
-        <v>534.1238071264848</v>
+        <v>534.1238071264844</v>
       </c>
       <c r="AC40" s="157" t="n">
-        <v>562.640845095134</v>
+        <v>562.6408450951337</v>
       </c>
       <c r="AD40" s="158" t="n">
-        <v>7428443.884957647</v>
+        <v>7428443.884957645</v>
       </c>
       <c r="AE40" s="159" t="n">
-        <v>8649579.032607021</v>
+        <v>8649579.032607017</v>
       </c>
       <c r="AF40" s="159" t="n">
-        <v>9011950.216916285</v>
+        <v>9011950.216916282</v>
       </c>
       <c r="AG40" s="159" t="n">
-        <v>10672385.86352629</v>
+        <v>10672385.86352628</v>
       </c>
       <c r="AH40" s="160" t="n">
         <v>12712332.24587731</v>
@@ -5020,49 +5020,49 @@
         </is>
       </c>
       <c r="C41" s="179" t="n">
-        <v>309.3136892127146</v>
+        <v>309.3136892127145</v>
       </c>
       <c r="D41" s="180" t="n">
         <v>355.8080302137847</v>
       </c>
       <c r="E41" s="180" t="n">
-        <v>395.0354675142579</v>
+        <v>395.0354675142577</v>
       </c>
       <c r="F41" s="180" t="n">
-        <v>432.9675524016264</v>
+        <v>432.9675524016262</v>
       </c>
       <c r="G41" s="181" t="n">
-        <v>463.3059453378227</v>
+        <v>463.3059453378225</v>
       </c>
       <c r="H41" s="179" t="n">
-        <v>45.3988501272089</v>
+        <v>45.39885012720887</v>
       </c>
       <c r="I41" s="180" t="n">
-        <v>48.84938984094185</v>
+        <v>48.84938984094184</v>
       </c>
       <c r="J41" s="180" t="n">
-        <v>52.92612094052871</v>
+        <v>52.92612094052868</v>
       </c>
       <c r="K41" s="180" t="n">
-        <v>61.04287458219935</v>
+        <v>61.04287458219931</v>
       </c>
       <c r="L41" s="181" t="n">
-        <v>68.14402902997155</v>
+        <v>68.14402902997153</v>
       </c>
       <c r="M41" s="182" t="n">
-        <v>26356373.57329554</v>
+        <v>26356373.57329553</v>
       </c>
       <c r="N41" s="183" t="n">
-        <v>28709179.20304899</v>
+        <v>28709179.20304898</v>
       </c>
       <c r="O41" s="183" t="n">
-        <v>31488911.90547825</v>
+        <v>31488911.90547824</v>
       </c>
       <c r="P41" s="183" t="n">
-        <v>36767856.60592005</v>
+        <v>36767856.60592002</v>
       </c>
       <c r="Q41" s="184" t="n">
-        <v>41704551.57206432</v>
+        <v>41704551.5720643</v>
       </c>
       <c r="S41" s="51" t="inlineStr">
         <is>
@@ -5070,49 +5070,49 @@
         </is>
       </c>
       <c r="T41" s="185" t="n">
-        <v>347.9569473438972</v>
+        <v>347.9569473438971</v>
       </c>
       <c r="U41" s="186" t="n">
-        <v>394.9640457169419</v>
+        <v>394.9640457169418</v>
       </c>
       <c r="V41" s="186" t="n">
-        <v>433.2626942151909</v>
+        <v>433.2626942151908</v>
       </c>
       <c r="W41" s="186" t="n">
-        <v>471.8380049288473</v>
+        <v>471.8380049288471</v>
       </c>
       <c r="X41" s="187" t="n">
-        <v>500.7740256700744</v>
+        <v>500.7740256700743</v>
       </c>
       <c r="Y41" s="185" t="n">
-        <v>51.07462240281318</v>
+        <v>51.07462240281315</v>
       </c>
       <c r="Z41" s="186" t="n">
-        <v>54.84452559409867</v>
+        <v>54.84452559409866</v>
       </c>
       <c r="AA41" s="186" t="n">
-        <v>59.32162973297365</v>
+        <v>59.32162973297362</v>
       </c>
       <c r="AB41" s="186" t="n">
-        <v>68.33799152025126</v>
+        <v>68.33799152025122</v>
       </c>
       <c r="AC41" s="187" t="n">
-        <v>76.1937966965538</v>
+        <v>76.19379669655378</v>
       </c>
       <c r="AD41" s="188" t="n">
-        <v>26356373.57329554</v>
+        <v>26356373.57329553</v>
       </c>
       <c r="AE41" s="189" t="n">
-        <v>28709179.20304899</v>
+        <v>28709179.20304898</v>
       </c>
       <c r="AF41" s="189" t="n">
-        <v>31488911.90547825</v>
+        <v>31488911.90547824</v>
       </c>
       <c r="AG41" s="189" t="n">
-        <v>36767856.60592005</v>
+        <v>36767856.60592002</v>
       </c>
       <c r="AH41" s="190" t="n">
-        <v>41704551.57206432</v>
+        <v>41704551.5720643</v>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1" thickBot="1"/>
@@ -6334,49 +6334,49 @@
         </is>
       </c>
       <c r="C57" s="148" t="n">
-        <v>0.4482224797210361</v>
+        <v>0.4482224797210358</v>
       </c>
       <c r="D57" s="149" t="n">
-        <v>0.06617348505642909</v>
+        <v>0.06617348505642899</v>
       </c>
       <c r="E57" s="149" t="n">
-        <v>0.05246753533845384</v>
+        <v>0.0524675353384538</v>
       </c>
       <c r="F57" s="149" t="n">
-        <v>0.03611980663748066</v>
+        <v>0.03611980663748065</v>
       </c>
       <c r="G57" s="150" t="n">
-        <v>0.02151480147994134</v>
+        <v>0.02151480147994132</v>
       </c>
       <c r="H57" s="148" t="n">
-        <v>0.08256592234039496</v>
+        <v>0.08256592234039492</v>
       </c>
       <c r="I57" s="149" t="n">
-        <v>0.01172635741609546</v>
+        <v>0.01172635741609544</v>
       </c>
       <c r="J57" s="149" t="n">
-        <v>0.00912458636917742</v>
+        <v>0.009124586369177411</v>
       </c>
       <c r="K57" s="149" t="n">
-        <v>0.006542738448540086</v>
+        <v>0.006542738448540084</v>
       </c>
       <c r="L57" s="150" t="n">
-        <v>0.003984357368889431</v>
+        <v>0.003984357368889427</v>
       </c>
       <c r="M57" s="151" t="n">
-        <v>24419.77128613649</v>
+        <v>24419.77128613648</v>
       </c>
       <c r="N57" s="152" t="n">
-        <v>3512.981078027557</v>
+        <v>3512.981078027551</v>
       </c>
       <c r="O57" s="152" t="n">
-        <v>2768.053604727735</v>
+        <v>2768.053604727732</v>
       </c>
       <c r="P57" s="152" t="n">
-        <v>2010.698402382617</v>
+        <v>2010.698402382616</v>
       </c>
       <c r="Q57" s="153" t="n">
-        <v>1245.763044370075</v>
+        <v>1245.763044370073</v>
       </c>
       <c r="S57" s="21" t="inlineStr">
         <is>
@@ -6384,49 +6384,49 @@
         </is>
       </c>
       <c r="T57" s="148" t="n">
-        <v>0.5513661926016877</v>
+        <v>0.5513661926016875</v>
       </c>
       <c r="U57" s="149" t="n">
-        <v>0.08140114375668078</v>
+        <v>0.08140114375668064</v>
       </c>
       <c r="V57" s="149" t="n">
-        <v>0.06454121893387069</v>
+        <v>0.06454121893387064</v>
       </c>
       <c r="W57" s="149" t="n">
-        <v>0.04443159628140851</v>
+        <v>0.04443159628140849</v>
       </c>
       <c r="X57" s="150" t="n">
-        <v>0.0264657278768334</v>
+        <v>0.02646572787683337</v>
       </c>
       <c r="Y57" s="148" t="n">
         <v>0.1024453007910956</v>
       </c>
       <c r="Z57" s="149" t="n">
-        <v>0.01455079123504026</v>
+        <v>0.01455079123504024</v>
       </c>
       <c r="AA57" s="149" t="n">
-        <v>0.01132274874581185</v>
+        <v>0.01132274874581184</v>
       </c>
       <c r="AB57" s="149" t="n">
-        <v>0.008118296457789054</v>
+        <v>0.008118296457789049</v>
       </c>
       <c r="AC57" s="150" t="n">
-        <v>0.00494361855388884</v>
+        <v>0.004943618553888836</v>
       </c>
       <c r="AD57" s="151" t="n">
-        <v>24419.77128613649</v>
+        <v>24419.77128613648</v>
       </c>
       <c r="AE57" s="152" t="n">
-        <v>3512.981078027557</v>
+        <v>3512.981078027551</v>
       </c>
       <c r="AF57" s="152" t="n">
-        <v>2768.053604727735</v>
+        <v>2768.053604727732</v>
       </c>
       <c r="AG57" s="152" t="n">
-        <v>2010.698402382617</v>
+        <v>2010.698402382616</v>
       </c>
       <c r="AH57" s="153" t="n">
-        <v>1245.763044370075</v>
+        <v>1245.763044370073</v>
       </c>
     </row>
     <row r="58" ht="15" customHeight="1" thickBot="1">
@@ -6436,49 +6436,49 @@
         </is>
       </c>
       <c r="C58" s="155" t="n">
-        <v>1.563430649798701</v>
+        <v>1.5634306497987</v>
       </c>
       <c r="D58" s="156" t="n">
-        <v>0.02940634731723226</v>
+        <v>0.02940634731723227</v>
       </c>
       <c r="E58" s="156" t="n">
-        <v>0.02572933705455119</v>
+        <v>0.02572933705455118</v>
       </c>
       <c r="F58" s="156" t="n">
-        <v>0.01783692681688848</v>
+        <v>0.01783692681688847</v>
       </c>
       <c r="G58" s="157" t="n">
-        <v>0.01048255266680703</v>
+        <v>0.01048255266680704</v>
       </c>
       <c r="H58" s="155" t="n">
-        <v>0.1285217416662356</v>
+        <v>0.1285217416662355</v>
       </c>
       <c r="I58" s="156" t="n">
-        <v>0.001956149480440259</v>
+        <v>0.00195614948044026</v>
       </c>
       <c r="J58" s="156" t="n">
-        <v>0.001530714831127044</v>
+        <v>0.001530714831127043</v>
       </c>
       <c r="K58" s="156" t="n">
         <v>0.001112151418622067</v>
       </c>
       <c r="L58" s="157" t="n">
-        <v>0.0006921598570196267</v>
+        <v>0.0006921598570196271</v>
       </c>
       <c r="M58" s="158" t="n">
-        <v>34870.492694787</v>
+        <v>34870.49269478698</v>
       </c>
       <c r="N58" s="159" t="n">
-        <v>535.0111726461537</v>
+        <v>535.0111726461539</v>
       </c>
       <c r="O58" s="159" t="n">
-        <v>421.8956008204516</v>
+        <v>421.8956008204513</v>
       </c>
       <c r="P58" s="159" t="n">
         <v>308.6559936695286</v>
       </c>
       <c r="Q58" s="160" t="n">
-        <v>193.8734921903524</v>
+        <v>193.8734921903526</v>
       </c>
       <c r="S58" s="32" t="inlineStr">
         <is>
@@ -6486,49 +6486,49 @@
         </is>
       </c>
       <c r="T58" s="155" t="n">
-        <v>1.859810032859679</v>
+        <v>1.859810032859678</v>
       </c>
       <c r="U58" s="156" t="n">
-        <v>0.03498090547053461</v>
+        <v>0.03498090547053462</v>
       </c>
       <c r="V58" s="156" t="n">
-        <v>0.03060684476093886</v>
+        <v>0.03060684476093884</v>
       </c>
       <c r="W58" s="156" t="n">
-        <v>0.0212182711485823</v>
+        <v>0.02121827114858229</v>
       </c>
       <c r="X58" s="157" t="n">
         <v>0.01246972906807082</v>
       </c>
       <c r="Y58" s="155" t="n">
-        <v>0.1344158608758303</v>
+        <v>0.1344158608758302</v>
       </c>
       <c r="Z58" s="156" t="n">
-        <v>0.002041645422390707</v>
+        <v>0.002041645422390708</v>
       </c>
       <c r="AA58" s="156" t="n">
-        <v>0.001596143027367506</v>
+        <v>0.001596143027367504</v>
       </c>
       <c r="AB58" s="156" t="n">
         <v>0.001160123869262823</v>
       </c>
       <c r="AC58" s="157" t="n">
-        <v>0.0007223649134025061</v>
+        <v>0.0007223649134025065</v>
       </c>
       <c r="AD58" s="158" t="n">
-        <v>34870.492694787</v>
+        <v>34870.49269478698</v>
       </c>
       <c r="AE58" s="159" t="n">
-        <v>535.0111726461537</v>
+        <v>535.0111726461539</v>
       </c>
       <c r="AF58" s="159" t="n">
-        <v>421.8956008204516</v>
+        <v>421.8956008204513</v>
       </c>
       <c r="AG58" s="159" t="n">
         <v>308.6559936695286</v>
       </c>
       <c r="AH58" s="160" t="n">
-        <v>193.8734921903524</v>
+        <v>193.8734921903526</v>
       </c>
     </row>
     <row r="59" ht="15" customHeight="1" thickTop="1">
@@ -6538,49 +6538,49 @@
         </is>
       </c>
       <c r="C59" s="161" t="n">
-        <v>0.772157516561421</v>
+        <v>0.7721575165614205</v>
       </c>
       <c r="D59" s="162" t="n">
-        <v>0.05678907987068528</v>
+        <v>0.05678907987068522</v>
       </c>
       <c r="E59" s="162" t="n">
-        <v>0.04612758969311258</v>
+        <v>0.04612758969311255</v>
       </c>
       <c r="F59" s="162" t="n">
-        <v>0.03178425633205065</v>
+        <v>0.03178425633205064</v>
       </c>
       <c r="G59" s="163" t="n">
-        <v>0.01884403201929678</v>
+        <v>0.01884403201929677</v>
       </c>
       <c r="H59" s="161" t="n">
         <v>0.1045534871842442</v>
       </c>
       <c r="I59" s="162" t="n">
-        <v>0.007063546815800387</v>
+        <v>0.007063546815800377</v>
       </c>
       <c r="J59" s="162" t="n">
-        <v>0.005509581950653443</v>
+        <v>0.005509581950653439</v>
       </c>
       <c r="K59" s="162" t="n">
-        <v>0.003965738058900081</v>
+        <v>0.003965738058900079</v>
       </c>
       <c r="L59" s="163" t="n">
-        <v>0.002428689148766427</v>
+        <v>0.002428689148766426</v>
       </c>
       <c r="M59" s="164" t="n">
-        <v>59290.26398092348</v>
+        <v>59290.26398092345</v>
       </c>
       <c r="N59" s="165" t="n">
-        <v>4047.99225067371</v>
+        <v>4047.992250673705</v>
       </c>
       <c r="O59" s="165" t="n">
-        <v>3189.949205548186</v>
+        <v>3189.949205548184</v>
       </c>
       <c r="P59" s="165" t="n">
-        <v>2319.354396052146</v>
+        <v>2319.354396052145</v>
       </c>
       <c r="Q59" s="166" t="n">
-        <v>1439.636536560427</v>
+        <v>1439.636536560426</v>
       </c>
       <c r="S59" s="42" t="inlineStr">
         <is>
@@ -6588,49 +6588,49 @@
         </is>
       </c>
       <c r="T59" s="161" t="n">
-        <v>0.9405321546448957</v>
+        <v>0.9405321546448953</v>
       </c>
       <c r="U59" s="162" t="n">
-        <v>0.06925470936499308</v>
+        <v>0.06925470936499298</v>
       </c>
       <c r="V59" s="162" t="n">
-        <v>0.05628742049200185</v>
+        <v>0.05628742049200182</v>
       </c>
       <c r="W59" s="162" t="n">
-        <v>0.03878486359605263</v>
+        <v>0.03878486359605261</v>
       </c>
       <c r="X59" s="163" t="n">
-        <v>0.02299065583378186</v>
+        <v>0.02299065583378184</v>
       </c>
       <c r="Y59" s="161" t="n">
-        <v>0.1191066620144831</v>
+        <v>0.119106662014483</v>
       </c>
       <c r="Z59" s="162" t="n">
-        <v>0.008040059697795972</v>
+        <v>0.008040059697795962</v>
       </c>
       <c r="AA59" s="162" t="n">
-        <v>0.006269674174468264</v>
+        <v>0.006269674174468259</v>
       </c>
       <c r="AB59" s="162" t="n">
-        <v>0.004514740694604595</v>
+        <v>0.004514740694604593</v>
       </c>
       <c r="AC59" s="163" t="n">
-        <v>0.002766502879534259</v>
+        <v>0.002766502879534257</v>
       </c>
       <c r="AD59" s="164" t="n">
-        <v>59290.26398092348</v>
+        <v>59290.26398092345</v>
       </c>
       <c r="AE59" s="165" t="n">
-        <v>4047.99225067371</v>
+        <v>4047.992250673705</v>
       </c>
       <c r="AF59" s="165" t="n">
-        <v>3189.949205548186</v>
+        <v>3189.949205548184</v>
       </c>
       <c r="AG59" s="165" t="n">
-        <v>2319.354396052146</v>
+        <v>2319.354396052145</v>
       </c>
       <c r="AH59" s="166" t="n">
-        <v>1439.636536560427</v>
+        <v>1439.636536560426</v>
       </c>
     </row>
     <row r="60" ht="15" customHeight="1" thickBot="1">
@@ -6640,28 +6640,28 @@
         </is>
       </c>
       <c r="C60" s="155" t="n">
-        <v>2.494665949115364</v>
+        <v>2.494665949115365</v>
       </c>
       <c r="D60" s="156" t="n">
-        <v>0.0003440101105646531</v>
+        <v>0.0003440101105646529</v>
       </c>
       <c r="E60" s="156" t="n">
-        <v>0.0003292655492887432</v>
+        <v>0.0003292655492887433</v>
       </c>
       <c r="F60" s="156" t="n">
-        <v>0.0002812452255069115</v>
+        <v>0.0002812452255069116</v>
       </c>
       <c r="G60" s="157" t="n">
-        <v>0.0002355867275857636</v>
+        <v>0.0002355867275857635</v>
       </c>
       <c r="H60" s="155" t="n">
-        <v>0.2123972881646269</v>
+        <v>0.212397288164627</v>
       </c>
       <c r="I60" s="156" t="n">
-        <v>2.532239061389768e-05</v>
+        <v>2.532239061389766e-05</v>
       </c>
       <c r="J60" s="156" t="n">
-        <v>2.321643942247123e-05</v>
+        <v>2.321643942247124e-05</v>
       </c>
       <c r="K60" s="156" t="n">
         <v>2.136196088669237e-05</v>
@@ -6670,7 +6670,7 @@
         <v>1.954813630406801e-05</v>
       </c>
       <c r="M60" s="158" t="n">
-        <v>904.2196818019838</v>
+        <v>904.2196818019839</v>
       </c>
       <c r="N60" s="159" t="n">
         <v>0.1089080105240784</v>
@@ -6679,10 +6679,10 @@
         <v>0.1008483369306052</v>
       </c>
       <c r="P60" s="159" t="n">
-        <v>0.09369305840467244</v>
+        <v>0.09369305840467246</v>
       </c>
       <c r="Q60" s="160" t="n">
-        <v>0.08681092033001454</v>
+        <v>0.08681092033001453</v>
       </c>
       <c r="S60" s="32" t="inlineStr">
         <is>
@@ -6693,25 +6693,25 @@
         <v>2.551448178178755</v>
       </c>
       <c r="U60" s="156" t="n">
-        <v>0.0003518402815360937</v>
+        <v>0.0003518402815360935</v>
       </c>
       <c r="V60" s="156" t="n">
-        <v>0.00033676011257848</v>
+        <v>0.0003367601125784801</v>
       </c>
       <c r="W60" s="156" t="n">
         <v>0.0002876467763130952</v>
       </c>
       <c r="X60" s="157" t="n">
-        <v>0.0002409490245036387</v>
+        <v>0.0002409490245036386</v>
       </c>
       <c r="Y60" s="155" t="n">
         <v>0.2156988696392523</v>
       </c>
       <c r="Z60" s="156" t="n">
-        <v>2.571372413396643e-05</v>
+        <v>2.571372413396642e-05</v>
       </c>
       <c r="AA60" s="156" t="n">
-        <v>2.357466388619354e-05</v>
+        <v>2.357466388619355e-05</v>
       </c>
       <c r="AB60" s="156" t="n">
         <v>2.169248213100054e-05</v>
@@ -6720,7 +6720,7 @@
         <v>1.985166833768916e-05</v>
       </c>
       <c r="AD60" s="158" t="n">
-        <v>904.2196818019838</v>
+        <v>904.2196818019839</v>
       </c>
       <c r="AE60" s="159" t="n">
         <v>0.1089080105240784</v>
@@ -6729,10 +6729,10 @@
         <v>0.1008483369306052</v>
       </c>
       <c r="AG60" s="159" t="n">
-        <v>0.09369305840467244</v>
+        <v>0.09369305840467246</v>
       </c>
       <c r="AH60" s="160" t="n">
-        <v>0.08681092033001454</v>
+        <v>0.08681092033001453</v>
       </c>
     </row>
     <row r="61" ht="15" customHeight="1" thickTop="1">
@@ -6742,49 +6742,49 @@
         </is>
       </c>
       <c r="C61" s="161" t="n">
-        <v>0.7802503422785634</v>
+        <v>0.780250342278563</v>
       </c>
       <c r="D61" s="162" t="n">
-        <v>0.0565394967481394</v>
+        <v>0.05653949674813933</v>
       </c>
       <c r="E61" s="162" t="n">
-        <v>0.04592564622401284</v>
+        <v>0.0459256462240128</v>
       </c>
       <c r="F61" s="162" t="n">
-        <v>0.03164108993301991</v>
+        <v>0.03164108993301989</v>
       </c>
       <c r="G61" s="163" t="n">
-        <v>0.01875470868914995</v>
+        <v>0.01875470868914994</v>
       </c>
       <c r="H61" s="161" t="n">
-        <v>0.1053570635198704</v>
+        <v>0.1053570635198703</v>
       </c>
       <c r="I61" s="162" t="n">
-        <v>0.007011119904813964</v>
+        <v>0.007011119904813954</v>
       </c>
       <c r="J61" s="162" t="n">
-        <v>0.005468726820778081</v>
+        <v>0.005468726820778078</v>
       </c>
       <c r="K61" s="162" t="n">
-        <v>0.003936378011077712</v>
+        <v>0.00393637801107771</v>
       </c>
       <c r="L61" s="163" t="n">
-        <v>0.002410774480896691</v>
+        <v>0.00241077448089669</v>
       </c>
       <c r="M61" s="164" t="n">
-        <v>60194.48366272547</v>
+        <v>60194.48366272544</v>
       </c>
       <c r="N61" s="165" t="n">
-        <v>4048.101158684234</v>
+        <v>4048.101158684229</v>
       </c>
       <c r="O61" s="165" t="n">
-        <v>3190.050053885117</v>
+        <v>3190.050053885114</v>
       </c>
       <c r="P61" s="165" t="n">
-        <v>2319.448089110551</v>
+        <v>2319.44808911055</v>
       </c>
       <c r="Q61" s="166" t="n">
-        <v>1439.723347480757</v>
+        <v>1439.723347480756</v>
       </c>
       <c r="S61" s="42" t="inlineStr">
         <is>
@@ -6792,49 +6792,49 @@
         </is>
       </c>
       <c r="T61" s="161" t="n">
-        <v>0.9495378173707686</v>
+        <v>0.9495378173707681</v>
       </c>
       <c r="U61" s="162" t="n">
-        <v>0.06889174216425432</v>
+        <v>0.06889174216425423</v>
       </c>
       <c r="V61" s="162" t="n">
-        <v>0.05599332250475066</v>
+        <v>0.05599332250475062</v>
       </c>
       <c r="W61" s="162" t="n">
-        <v>0.03857631211072681</v>
+        <v>0.0385763121107268</v>
       </c>
       <c r="X61" s="163" t="n">
-        <v>0.02286050952639389</v>
+        <v>0.02286050952639387</v>
       </c>
       <c r="Y61" s="161" t="n">
         <v>0.1199133003188764</v>
       </c>
       <c r="Z61" s="162" t="n">
-        <v>0.007973203080319223</v>
+        <v>0.007973203080319213</v>
       </c>
       <c r="AA61" s="162" t="n">
-        <v>0.006217595835888401</v>
+        <v>0.006217595835888397</v>
       </c>
       <c r="AB61" s="162" t="n">
-        <v>0.004477280597217064</v>
+        <v>0.004477280597217062</v>
       </c>
       <c r="AC61" s="163" t="n">
-        <v>0.002743613984729004</v>
+        <v>0.002743613984729002</v>
       </c>
       <c r="AD61" s="164" t="n">
-        <v>60194.48366272547</v>
+        <v>60194.48366272544</v>
       </c>
       <c r="AE61" s="165" t="n">
-        <v>4048.101158684234</v>
+        <v>4048.101158684229</v>
       </c>
       <c r="AF61" s="165" t="n">
-        <v>3190.050053885117</v>
+        <v>3190.050053885114</v>
       </c>
       <c r="AG61" s="165" t="n">
-        <v>2319.448089110551</v>
+        <v>2319.44808911055</v>
       </c>
       <c r="AH61" s="166" t="n">
-        <v>1439.723347480757</v>
+        <v>1439.723347480756</v>
       </c>
     </row>
     <row r="62" ht="15" customHeight="1" thickBot="1">
@@ -6844,10 +6844,10 @@
         </is>
       </c>
       <c r="C62" s="155" t="n">
-        <v>2.343143258645738</v>
+        <v>2.343143258645737</v>
       </c>
       <c r="D62" s="156" t="n">
-        <v>0.007332213935871513</v>
+        <v>0.007332213935871509</v>
       </c>
       <c r="E62" s="156" t="n">
         <v>0</v>
@@ -6859,10 +6859,10 @@
         <v>0</v>
       </c>
       <c r="H62" s="155" t="n">
-        <v>2.05014717978564</v>
+        <v>2.050147179785639</v>
       </c>
       <c r="I62" s="156" t="n">
-        <v>0.006454793054520389</v>
+        <v>0.006454793054520386</v>
       </c>
       <c r="J62" s="156" t="n">
         <v>0</v>
@@ -6874,10 +6874,10 @@
         <v>0</v>
       </c>
       <c r="M62" s="158" t="n">
-        <v>18889.36835995101</v>
+        <v>18889.368359951</v>
       </c>
       <c r="N62" s="159" t="n">
-        <v>66.64626502818012</v>
+        <v>66.64626502818008</v>
       </c>
       <c r="O62" s="159" t="n">
         <v>0</v>
@@ -6894,10 +6894,10 @@
         </is>
       </c>
       <c r="T62" s="155" t="n">
-        <v>1.529179008813401</v>
+        <v>1.5291790088134</v>
       </c>
       <c r="U62" s="156" t="n">
-        <v>0.004785139618541351</v>
+        <v>0.004785139618541348</v>
       </c>
       <c r="V62" s="156" t="n">
         <v>0</v>
@@ -6909,10 +6909,10 @@
         <v>0</v>
       </c>
       <c r="Y62" s="155" t="n">
-        <v>1.344132587536298</v>
+        <v>1.344132587536297</v>
       </c>
       <c r="Z62" s="156" t="n">
-        <v>0.004231100087015821</v>
+        <v>0.004231100087015818</v>
       </c>
       <c r="AA62" s="156" t="n">
         <v>0</v>
@@ -6924,10 +6924,10 @@
         <v>0</v>
       </c>
       <c r="AD62" s="158" t="n">
-        <v>18889.36835995101</v>
+        <v>18889.368359951</v>
       </c>
       <c r="AE62" s="159" t="n">
-        <v>66.64626502818012</v>
+        <v>66.64626502818008</v>
       </c>
       <c r="AF62" s="159" t="n">
         <v>0</v>
@@ -6946,49 +6946,49 @@
         </is>
       </c>
       <c r="C63" s="179" t="n">
-        <v>0.9281139515745538</v>
+        <v>0.9281139515745535</v>
       </c>
       <c r="D63" s="180" t="n">
-        <v>0.05099623940146893</v>
+        <v>0.05099623940146888</v>
       </c>
       <c r="E63" s="180" t="n">
-        <v>0.04001989393006469</v>
+        <v>0.04001989393006466</v>
       </c>
       <c r="F63" s="180" t="n">
-        <v>0.0273131440004346</v>
+        <v>0.02731314400043459</v>
       </c>
       <c r="G63" s="181" t="n">
-        <v>0.01599423471505006</v>
+        <v>0.01599423471505005</v>
       </c>
       <c r="H63" s="179" t="n">
-        <v>0.1362219250488083</v>
+        <v>0.1362219250488082</v>
       </c>
       <c r="I63" s="180" t="n">
-        <v>0.007001346140073271</v>
+        <v>0.007001346140073261</v>
       </c>
       <c r="J63" s="180" t="n">
-        <v>0.005361791333567502</v>
+        <v>0.005361791333567498</v>
       </c>
       <c r="K63" s="180" t="n">
-        <v>0.003850803170851693</v>
+        <v>0.003850803170851692</v>
       </c>
       <c r="L63" s="181" t="n">
-        <v>0.002352466238998581</v>
+        <v>0.00235246623899858</v>
       </c>
       <c r="M63" s="182" t="n">
-        <v>79083.85202267648</v>
+        <v>79083.85202267645</v>
       </c>
       <c r="N63" s="183" t="n">
-        <v>4114.747423712414</v>
+        <v>4114.747423712409</v>
       </c>
       <c r="O63" s="183" t="n">
-        <v>3190.050053885117</v>
+        <v>3190.050053885114</v>
       </c>
       <c r="P63" s="183" t="n">
-        <v>2319.448089110551</v>
+        <v>2319.44808911055</v>
       </c>
       <c r="Q63" s="184" t="n">
-        <v>1439.723347480757</v>
+        <v>1439.723347480756</v>
       </c>
       <c r="S63" s="51" t="inlineStr">
         <is>
@@ -6996,49 +6996,49 @@
         </is>
       </c>
       <c r="T63" s="185" t="n">
-        <v>1.044065324748933</v>
+        <v>1.044065324748932</v>
       </c>
       <c r="U63" s="186" t="n">
-        <v>0.05660828120785219</v>
+        <v>0.05660828120785211</v>
       </c>
       <c r="V63" s="186" t="n">
-        <v>0.04389258305197666</v>
+        <v>0.04389258305197664</v>
       </c>
       <c r="W63" s="186" t="n">
-        <v>0.02976523137129887</v>
+        <v>0.02976523137129886</v>
       </c>
       <c r="X63" s="187" t="n">
-        <v>0.01728770672244988</v>
+        <v>0.01728770672244987</v>
       </c>
       <c r="Y63" s="185" t="n">
         <v>0.1532524142210018</v>
       </c>
       <c r="Z63" s="186" t="n">
-        <v>0.007860599872847642</v>
+        <v>0.007860599872847632</v>
       </c>
       <c r="AA63" s="186" t="n">
-        <v>0.006009701722761111</v>
+        <v>0.006009701722761107</v>
       </c>
       <c r="AB63" s="186" t="n">
-        <v>0.004311005276815034</v>
+        <v>0.004311005276815032</v>
       </c>
       <c r="AC63" s="187" t="n">
-        <v>0.002630360090257189</v>
+        <v>0.002630360090257187</v>
       </c>
       <c r="AD63" s="188" t="n">
-        <v>79083.85202267648</v>
+        <v>79083.85202267645</v>
       </c>
       <c r="AE63" s="189" t="n">
-        <v>4114.747423712414</v>
+        <v>4114.747423712409</v>
       </c>
       <c r="AF63" s="189" t="n">
-        <v>3190.050053885117</v>
+        <v>3190.050053885114</v>
       </c>
       <c r="AG63" s="189" t="n">
-        <v>2319.448089110551</v>
+        <v>2319.44808911055</v>
       </c>
       <c r="AH63" s="190" t="n">
-        <v>1439.723347480757</v>
+        <v>1439.723347480756</v>
       </c>
     </row>
     <row r="64" ht="15" customHeight="1" thickBot="1"/>
@@ -7300,46 +7300,46 @@
         <v>1.123920845769233</v>
       </c>
       <c r="D68" s="149" t="n">
-        <v>1.072741376113453</v>
+        <v>1.072741376113451</v>
       </c>
       <c r="E68" s="149" t="n">
         <v>1.349020985944958</v>
       </c>
       <c r="F68" s="149" t="n">
-        <v>0.6734473024225879</v>
+        <v>0.6734473024225878</v>
       </c>
       <c r="G68" s="150" t="n">
-        <v>0.6979040574879253</v>
+        <v>0.6979040574879249</v>
       </c>
       <c r="H68" s="148" t="n">
-        <v>0.2070345988141619</v>
+        <v>0.2070345988141618</v>
       </c>
       <c r="I68" s="149" t="n">
-        <v>0.190096513439083</v>
+        <v>0.1900965134390828</v>
       </c>
       <c r="J68" s="149" t="n">
-        <v>0.2346071417436318</v>
+        <v>0.2346071417436316</v>
       </c>
       <c r="K68" s="149" t="n">
-        <v>0.1219881823523848</v>
+        <v>0.1219881823523847</v>
       </c>
       <c r="L68" s="150" t="n">
         <v>0.1292458671683467</v>
       </c>
       <c r="M68" s="151" t="n">
-        <v>61232.73873833254</v>
+        <v>61232.73873833252</v>
       </c>
       <c r="N68" s="152" t="n">
-        <v>56949.09604186957</v>
+        <v>56949.0960418695</v>
       </c>
       <c r="O68" s="152" t="n">
-        <v>71170.91319251487</v>
+        <v>71170.91319251482</v>
       </c>
       <c r="P68" s="152" t="n">
         <v>37489.11030063112</v>
       </c>
       <c r="Q68" s="153" t="n">
-        <v>40410.4627293431</v>
+        <v>40410.46272934308</v>
       </c>
       <c r="S68" s="21" t="inlineStr">
         <is>
@@ -7347,49 +7347,49 @@
         </is>
       </c>
       <c r="T68" s="148" t="n">
-        <v>1.382554391076355</v>
+        <v>1.382554391076354</v>
       </c>
       <c r="U68" s="149" t="n">
-        <v>1.319597643924708</v>
+        <v>1.319597643924707</v>
       </c>
       <c r="V68" s="149" t="n">
-        <v>1.659453950688003</v>
+        <v>1.659453950688002</v>
       </c>
       <c r="W68" s="149" t="n">
-        <v>0.8284191263359186</v>
+        <v>0.8284191263359185</v>
       </c>
       <c r="X68" s="150" t="n">
-        <v>0.8585038019910969</v>
+        <v>0.8585038019910965</v>
       </c>
       <c r="Y68" s="148" t="n">
-        <v>0.2568822723524991</v>
+        <v>0.2568822723524989</v>
       </c>
       <c r="Z68" s="149" t="n">
-        <v>0.235883538545778</v>
+        <v>0.2358835385457776</v>
       </c>
       <c r="AA68" s="149" t="n">
-        <v>0.291125275432697</v>
+        <v>0.2911252754326968</v>
       </c>
       <c r="AB68" s="149" t="n">
-        <v>0.1513641782370911</v>
+        <v>0.151364178237091</v>
       </c>
       <c r="AC68" s="150" t="n">
-        <v>0.1603626903389405</v>
+        <v>0.1603626903389404</v>
       </c>
       <c r="AD68" s="151" t="n">
-        <v>61232.73873833254</v>
+        <v>61232.73873833252</v>
       </c>
       <c r="AE68" s="152" t="n">
-        <v>56949.09604186957</v>
+        <v>56949.0960418695</v>
       </c>
       <c r="AF68" s="152" t="n">
-        <v>71170.91319251487</v>
+        <v>71170.91319251482</v>
       </c>
       <c r="AG68" s="152" t="n">
         <v>37489.11030063112</v>
       </c>
       <c r="AH68" s="153" t="n">
-        <v>40410.4627293431</v>
+        <v>40410.46272934308</v>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1" thickBot="1">
@@ -7399,49 +7399,49 @@
         </is>
       </c>
       <c r="C69" s="155" t="n">
-        <v>2.851685782840009</v>
+        <v>2.851685782840007</v>
       </c>
       <c r="D69" s="156" t="n">
-        <v>2.768668656180178</v>
+        <v>2.76866865618018</v>
       </c>
       <c r="E69" s="156" t="n">
-        <v>3.973443174630005</v>
+        <v>3.973443174630003</v>
       </c>
       <c r="F69" s="156" t="n">
-        <v>0.8115646454014095</v>
+        <v>0.811564645401409</v>
       </c>
       <c r="G69" s="157" t="n">
-        <v>0.8946734527412955</v>
+        <v>0.8946734527412963</v>
       </c>
       <c r="H69" s="155" t="n">
-        <v>0.2344226931604733</v>
+        <v>0.2344226931604732</v>
       </c>
       <c r="I69" s="156" t="n">
-        <v>0.1841755351275582</v>
+        <v>0.1841755351275583</v>
       </c>
       <c r="J69" s="156" t="n">
-        <v>0.236391959308987</v>
+        <v>0.2363919593089868</v>
       </c>
       <c r="K69" s="156" t="n">
-        <v>0.05060192156151602</v>
+        <v>0.05060192156151599</v>
       </c>
       <c r="L69" s="157" t="n">
-        <v>0.05907502388130575</v>
+        <v>0.0590750238813058</v>
       </c>
       <c r="M69" s="158" t="n">
-        <v>63603.51722102529</v>
+        <v>63603.51722102526</v>
       </c>
       <c r="N69" s="159" t="n">
-        <v>50372.41274585562</v>
+        <v>50372.41274585565</v>
       </c>
       <c r="O69" s="159" t="n">
-        <v>65154.34859173407</v>
+        <v>65154.34859173402</v>
       </c>
       <c r="P69" s="159" t="n">
-        <v>14043.57906633648</v>
+        <v>14043.57906633647</v>
       </c>
       <c r="Q69" s="160" t="n">
-        <v>16546.87290073867</v>
+        <v>16546.87290073869</v>
       </c>
       <c r="S69" s="32" t="inlineStr">
         <is>
@@ -7449,49 +7449,49 @@
         </is>
       </c>
       <c r="T69" s="155" t="n">
-        <v>3.392279555330464</v>
+        <v>3.392279555330462</v>
       </c>
       <c r="U69" s="156" t="n">
-        <v>3.293524880742874</v>
+        <v>3.293524880742876</v>
       </c>
       <c r="V69" s="156" t="n">
-        <v>4.726688377336196</v>
+        <v>4.726688377336195</v>
       </c>
       <c r="W69" s="156" t="n">
-        <v>0.9654128694650357</v>
+        <v>0.9654128694650352</v>
       </c>
       <c r="X69" s="157" t="n">
-        <v>1.064276604629511</v>
+        <v>1.064276604629512</v>
       </c>
       <c r="Y69" s="155" t="n">
-        <v>0.2451735224054607</v>
+        <v>0.2451735224054605</v>
       </c>
       <c r="Z69" s="156" t="n">
-        <v>0.1922251555770212</v>
+        <v>0.1922251555770213</v>
       </c>
       <c r="AA69" s="156" t="n">
-        <v>0.2464961924351191</v>
+        <v>0.2464961924351189</v>
       </c>
       <c r="AB69" s="156" t="n">
-        <v>0.05278462631177824</v>
+        <v>0.05278462631177822</v>
       </c>
       <c r="AC69" s="157" t="n">
-        <v>0.06165298966342737</v>
+        <v>0.06165298966342742</v>
       </c>
       <c r="AD69" s="158" t="n">
-        <v>63603.51722102529</v>
+        <v>63603.51722102526</v>
       </c>
       <c r="AE69" s="159" t="n">
-        <v>50372.41274585562</v>
+        <v>50372.41274585565</v>
       </c>
       <c r="AF69" s="159" t="n">
-        <v>65154.34859173407</v>
+        <v>65154.34859173402</v>
       </c>
       <c r="AG69" s="159" t="n">
-        <v>14043.57906633648</v>
+        <v>14043.57906633647</v>
       </c>
       <c r="AH69" s="160" t="n">
-        <v>16546.87290073867</v>
+        <v>16546.87290073869</v>
       </c>
     </row>
     <row r="70" ht="15" customHeight="1" thickTop="1">
@@ -7501,31 +7501,31 @@
         </is>
       </c>
       <c r="C70" s="161" t="n">
-        <v>1.625785532164572</v>
+        <v>1.625785532164571</v>
       </c>
       <c r="D70" s="162" t="n">
         <v>1.505608053813402</v>
       </c>
       <c r="E70" s="162" t="n">
-        <v>1.971302781076526</v>
+        <v>1.971302781076525</v>
       </c>
       <c r="F70" s="162" t="n">
-        <v>0.706200057700373</v>
+        <v>0.7062000577003728</v>
       </c>
       <c r="G70" s="163" t="n">
         <v>0.7455394671431663</v>
       </c>
       <c r="H70" s="161" t="n">
-        <v>0.2201384343941397</v>
+        <v>0.2201384343941396</v>
       </c>
       <c r="I70" s="162" t="n">
         <v>0.1872707393494301</v>
       </c>
       <c r="J70" s="162" t="n">
-        <v>0.2354567904837624</v>
+        <v>0.2354567904837622</v>
       </c>
       <c r="K70" s="162" t="n">
-        <v>0.0881129455023846</v>
+        <v>0.08811294550238458</v>
       </c>
       <c r="L70" s="163" t="n">
         <v>0.0960879079367688</v>
@@ -7534,13 +7534,13 @@
         <v>124836.2559593578</v>
       </c>
       <c r="N70" s="165" t="n">
-        <v>107321.5087877252</v>
+        <v>107321.5087877251</v>
       </c>
       <c r="O70" s="165" t="n">
-        <v>136325.2617842489</v>
+        <v>136325.2617842488</v>
       </c>
       <c r="P70" s="165" t="n">
-        <v>51532.6893669676</v>
+        <v>51532.68936696758</v>
       </c>
       <c r="Q70" s="166" t="n">
         <v>56957.33563008177</v>
@@ -7551,28 +7551,28 @@
         </is>
       </c>
       <c r="T70" s="161" t="n">
-        <v>1.980300051169173</v>
+        <v>1.980300051169172</v>
       </c>
       <c r="U70" s="162" t="n">
         <v>1.836100328124259</v>
       </c>
       <c r="V70" s="162" t="n">
-        <v>2.405492012344941</v>
+        <v>2.405492012344939</v>
       </c>
       <c r="W70" s="162" t="n">
-        <v>0.8617433934363921</v>
+        <v>0.8617433934363918</v>
       </c>
       <c r="X70" s="163" t="n">
         <v>0.9095952120033227</v>
       </c>
       <c r="Y70" s="161" t="n">
-        <v>0.250780292536541</v>
+        <v>0.2507802925365409</v>
       </c>
       <c r="Z70" s="162" t="n">
-        <v>0.2131603234584348</v>
+        <v>0.2131603234584347</v>
       </c>
       <c r="AA70" s="162" t="n">
-        <v>0.2679399946713101</v>
+        <v>0.2679399946713099</v>
       </c>
       <c r="AB70" s="162" t="n">
         <v>0.1003109874814643</v>
@@ -7584,13 +7584,13 @@
         <v>124836.2559593578</v>
       </c>
       <c r="AE70" s="165" t="n">
-        <v>107321.5087877252</v>
+        <v>107321.5087877251</v>
       </c>
       <c r="AF70" s="165" t="n">
-        <v>136325.2617842489</v>
+        <v>136325.2617842488</v>
       </c>
       <c r="AG70" s="165" t="n">
-        <v>51532.6893669676</v>
+        <v>51532.68936696758</v>
       </c>
       <c r="AH70" s="166" t="n">
         <v>56957.33563008177</v>
@@ -7606,13 +7606,13 @@
         <v>3.742731586234089</v>
       </c>
       <c r="D71" s="156" t="n">
-        <v>3.012669197828391</v>
+        <v>3.012669197828389</v>
       </c>
       <c r="E71" s="156" t="n">
-        <v>4.013047925171324</v>
+        <v>4.013047925171325</v>
       </c>
       <c r="F71" s="156" t="n">
-        <v>3.49301565873745</v>
+        <v>3.493015658737451</v>
       </c>
       <c r="G71" s="157" t="n">
         <v>3.880870744388005</v>
@@ -7621,13 +7621,13 @@
         <v>0.3186583115571484</v>
       </c>
       <c r="I71" s="156" t="n">
-        <v>0.2217608839828873</v>
+        <v>0.2217608839828872</v>
       </c>
       <c r="J71" s="156" t="n">
         <v>0.2829591017203911</v>
       </c>
       <c r="K71" s="156" t="n">
-        <v>0.2653117532717713</v>
+        <v>0.2653117532717714</v>
       </c>
       <c r="L71" s="157" t="n">
         <v>0.3220206463547441</v>
@@ -7636,7 +7636,7 @@
         <v>1356.595084474101</v>
       </c>
       <c r="N71" s="159" t="n">
-        <v>953.7621093871825</v>
+        <v>953.7621093871819</v>
       </c>
       <c r="O71" s="159" t="n">
         <v>1229.127098630783</v>
@@ -7656,22 +7656,22 @@
         <v>3.82792160629577</v>
       </c>
       <c r="U71" s="156" t="n">
-        <v>3.081241935009485</v>
+        <v>3.081241935009483</v>
       </c>
       <c r="V71" s="156" t="n">
         <v>4.104390738669158</v>
       </c>
       <c r="W71" s="156" t="n">
-        <v>3.572521780720144</v>
+        <v>3.572521780720145</v>
       </c>
       <c r="X71" s="157" t="n">
-        <v>3.969205012810354</v>
+        <v>3.969205012810353</v>
       </c>
       <c r="Y71" s="155" t="n">
         <v>0.3236116534160003</v>
       </c>
       <c r="Z71" s="156" t="n">
-        <v>0.2251879880294916</v>
+        <v>0.2251879880294915</v>
       </c>
       <c r="AA71" s="156" t="n">
         <v>0.2873250973248258</v>
@@ -7680,13 +7680,13 @@
         <v>0.2694167683163217</v>
       </c>
       <c r="AC71" s="157" t="n">
-        <v>0.3270207947134249</v>
+        <v>0.3270207947134248</v>
       </c>
       <c r="AD71" s="158" t="n">
         <v>1356.595084474101</v>
       </c>
       <c r="AE71" s="159" t="n">
-        <v>953.7621093871825</v>
+        <v>953.7621093871819</v>
       </c>
       <c r="AF71" s="159" t="n">
         <v>1229.127098630783</v>
@@ -7711,25 +7711,25 @@
         <v>1.512271824941497</v>
       </c>
       <c r="E72" s="162" t="n">
-        <v>1.980305667210989</v>
+        <v>1.980305667210988</v>
       </c>
       <c r="F72" s="162" t="n">
-        <v>0.7188648265700475</v>
+        <v>0.7188648265700472</v>
       </c>
       <c r="G72" s="163" t="n">
         <v>0.7605895278229671</v>
       </c>
       <c r="H72" s="161" t="n">
-        <v>0.2208725353916685</v>
+        <v>0.2208725353916684</v>
       </c>
       <c r="I72" s="162" t="n">
-        <v>0.1875276524049639</v>
+        <v>0.1875276524049638</v>
       </c>
       <c r="J72" s="162" t="n">
-        <v>0.235810524315564</v>
+        <v>0.2358105243155639</v>
       </c>
       <c r="K72" s="162" t="n">
-        <v>0.08943192861679816</v>
+        <v>0.08943192861679813</v>
       </c>
       <c r="L72" s="163" t="n">
         <v>0.0977679714734071</v>
@@ -7738,13 +7738,13 @@
         <v>126192.8510438319</v>
       </c>
       <c r="N72" s="165" t="n">
-        <v>108275.2708971124</v>
+        <v>108275.2708971123</v>
       </c>
       <c r="O72" s="165" t="n">
-        <v>137554.3888828797</v>
+        <v>137554.3888828796</v>
       </c>
       <c r="P72" s="165" t="n">
-        <v>52696.34048151596</v>
+        <v>52696.34048151594</v>
       </c>
       <c r="Q72" s="166" t="n">
         <v>58387.3905591291</v>
@@ -7755,31 +7755,31 @@
         </is>
       </c>
       <c r="T72" s="161" t="n">
-        <v>1.99062899217382</v>
+        <v>1.990628992173819</v>
       </c>
       <c r="U72" s="162" t="n">
-        <v>1.842659497134001</v>
+        <v>1.842659497134</v>
       </c>
       <c r="V72" s="162" t="n">
-        <v>2.414422071303446</v>
+        <v>2.414422071303445</v>
       </c>
       <c r="W72" s="162" t="n">
-        <v>0.8764285292919085</v>
+        <v>0.8764285292919083</v>
       </c>
       <c r="X72" s="163" t="n">
         <v>0.9270985987924958</v>
       </c>
       <c r="Y72" s="161" t="n">
-        <v>0.2513885048022207</v>
+        <v>0.2513885048022206</v>
       </c>
       <c r="Z72" s="162" t="n">
-        <v>0.2132606596520567</v>
+        <v>0.2132606596520566</v>
       </c>
       <c r="AA72" s="162" t="n">
-        <v>0.2681016225700787</v>
+        <v>0.2681016225700785</v>
       </c>
       <c r="AB72" s="162" t="n">
-        <v>0.1017208808810682</v>
+        <v>0.1017208808810681</v>
       </c>
       <c r="AC72" s="163" t="n">
         <v>0.1112661412000904</v>
@@ -7788,13 +7788,13 @@
         <v>126192.8510438319</v>
       </c>
       <c r="AE72" s="165" t="n">
-        <v>108275.2708971124</v>
+        <v>108275.2708971123</v>
       </c>
       <c r="AF72" s="165" t="n">
-        <v>137554.3888828797</v>
+        <v>137554.3888828796</v>
       </c>
       <c r="AG72" s="165" t="n">
-        <v>52696.34048151596</v>
+        <v>52696.34048151594</v>
       </c>
       <c r="AH72" s="166" t="n">
         <v>58387.3905591291</v>
@@ -7807,49 +7807,49 @@
         </is>
       </c>
       <c r="C73" s="155" t="n">
-        <v>53.60907303027516</v>
+        <v>53.60907303027513</v>
       </c>
       <c r="D73" s="156" t="n">
-        <v>67.62602560796522</v>
+        <v>67.62602560796515</v>
       </c>
       <c r="E73" s="156" t="n">
         <v>19.33166872100499</v>
       </c>
       <c r="F73" s="156" t="n">
-        <v>20.95140155930896</v>
+        <v>20.95140155930895</v>
       </c>
       <c r="G73" s="157" t="n">
-        <v>22.61989492637709</v>
+        <v>22.61989492637708</v>
       </c>
       <c r="H73" s="155" t="n">
-        <v>46.90557842693045</v>
+        <v>46.90557842693043</v>
       </c>
       <c r="I73" s="156" t="n">
-        <v>59.53345118089871</v>
+        <v>59.53345118089865</v>
       </c>
       <c r="J73" s="156" t="n">
         <v>17.03286278560236</v>
       </c>
       <c r="K73" s="156" t="n">
-        <v>18.58548072111208</v>
+        <v>18.58548072111207</v>
       </c>
       <c r="L73" s="157" t="n">
-        <v>20.24652483881342</v>
+        <v>20.2465248388134</v>
       </c>
       <c r="M73" s="158" t="n">
-        <v>432172.2644007935</v>
+        <v>432172.2644007933</v>
       </c>
       <c r="N73" s="159" t="n">
-        <v>614687.7416411933</v>
+        <v>614687.7416411927</v>
       </c>
       <c r="O73" s="159" t="n">
         <v>198157.6575402865</v>
       </c>
       <c r="P73" s="159" t="n">
-        <v>243364.0560568463</v>
+        <v>243364.0560568462</v>
       </c>
       <c r="Q73" s="160" t="n">
-        <v>299695.0017220365</v>
+        <v>299695.0017220362</v>
       </c>
       <c r="S73" s="32" t="inlineStr">
         <is>
@@ -7857,10 +7857,10 @@
         </is>
       </c>
       <c r="T73" s="155" t="n">
-        <v>34.98628129430805</v>
+        <v>34.98628129430803</v>
       </c>
       <c r="U73" s="156" t="n">
-        <v>44.13400607393801</v>
+        <v>44.13400607393797</v>
       </c>
       <c r="V73" s="156" t="n">
         <v>12.61620769640055</v>
@@ -7869,13 +7869,13 @@
         <v>13.67327556755228</v>
       </c>
       <c r="X73" s="157" t="n">
-        <v>14.76216546954642</v>
+        <v>14.76216546954641</v>
       </c>
       <c r="Y73" s="155" t="n">
-        <v>30.7525806549503</v>
+        <v>30.75258065495028</v>
       </c>
       <c r="Z73" s="156" t="n">
-        <v>39.02402266722538</v>
+        <v>39.02402266722535</v>
       </c>
       <c r="AA73" s="156" t="n">
         <v>11.16468761072311</v>
@@ -7884,22 +7884,22 @@
         <v>12.17970731203274</v>
       </c>
       <c r="AC73" s="157" t="n">
-        <v>13.26433621921414</v>
+        <v>13.26433621921413</v>
       </c>
       <c r="AD73" s="158" t="n">
-        <v>432172.2644007935</v>
+        <v>432172.2644007933</v>
       </c>
       <c r="AE73" s="159" t="n">
-        <v>614687.7416411933</v>
+        <v>614687.7416411927</v>
       </c>
       <c r="AF73" s="159" t="n">
         <v>198157.6575402865</v>
       </c>
       <c r="AG73" s="159" t="n">
-        <v>243364.0560568463</v>
+        <v>243364.0560568462</v>
       </c>
       <c r="AH73" s="160" t="n">
-        <v>299695.0017220365</v>
+        <v>299695.0017220362</v>
       </c>
     </row>
     <row r="74" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -7909,49 +7909,49 @@
         </is>
       </c>
       <c r="C74" s="179" t="n">
-        <v>6.552873190447237</v>
+        <v>6.552873190447234</v>
       </c>
       <c r="D74" s="180" t="n">
-        <v>8.960062688986913</v>
+        <v>8.960062688986907</v>
       </c>
       <c r="E74" s="180" t="n">
-        <v>4.211582972667646</v>
+        <v>4.211582972667645</v>
       </c>
       <c r="F74" s="180" t="n">
-        <v>3.486320854276573</v>
+        <v>3.48632085427657</v>
       </c>
       <c r="G74" s="181" t="n">
-        <v>3.978023860968291</v>
+        <v>3.978023860968288</v>
       </c>
       <c r="H74" s="179" t="n">
-        <v>0.9617838403237751</v>
+        <v>0.9617838403237747</v>
       </c>
       <c r="I74" s="180" t="n">
-        <v>1.230139733020119</v>
+        <v>1.230139733020118</v>
       </c>
       <c r="J74" s="180" t="n">
-        <v>0.5642600933153783</v>
+        <v>0.5642600933153781</v>
       </c>
       <c r="K74" s="180" t="n">
-        <v>0.4915265485379857</v>
+        <v>0.4915265485379854</v>
       </c>
       <c r="L74" s="181" t="n">
-        <v>0.5850962548431877</v>
+        <v>0.5850962548431874</v>
       </c>
       <c r="M74" s="182" t="n">
-        <v>558365.1154446254</v>
+        <v>558365.1154446251</v>
       </c>
       <c r="N74" s="183" t="n">
-        <v>722963.0125383057</v>
+        <v>722963.012538305</v>
       </c>
       <c r="O74" s="183" t="n">
-        <v>335712.0464231662</v>
+        <v>335712.0464231661</v>
       </c>
       <c r="P74" s="183" t="n">
-        <v>296060.3965383623</v>
+        <v>296060.3965383621</v>
       </c>
       <c r="Q74" s="184" t="n">
-        <v>358082.3922811656</v>
+        <v>358082.3922811653</v>
       </c>
       <c r="S74" s="51" t="inlineStr">
         <is>
@@ -7959,49 +7959,49 @@
         </is>
       </c>
       <c r="T74" s="185" t="n">
-        <v>7.371538445269556</v>
+        <v>7.371538445269553</v>
       </c>
       <c r="U74" s="186" t="n">
-        <v>9.946101012372791</v>
+        <v>9.946101012372782</v>
       </c>
       <c r="V74" s="186" t="n">
-        <v>4.619134066950452</v>
+        <v>4.619134066950451</v>
       </c>
       <c r="W74" s="186" t="n">
-        <v>3.799311674279436</v>
+        <v>3.799311674279434</v>
       </c>
       <c r="X74" s="187" t="n">
-        <v>4.2997311886774</v>
+        <v>4.299731188677398</v>
       </c>
       <c r="Y74" s="185" t="n">
-        <v>1.082026226215444</v>
+        <v>1.082026226215443</v>
       </c>
       <c r="Z74" s="186" t="n">
-        <v>1.38111100858407</v>
+        <v>1.381111008584068</v>
       </c>
       <c r="AA74" s="186" t="n">
-        <v>0.6324443910476704</v>
+        <v>0.6324443910476701</v>
       </c>
       <c r="AB74" s="186" t="n">
-        <v>0.5502679442255881</v>
+        <v>0.5502679442255878</v>
       </c>
       <c r="AC74" s="187" t="n">
-        <v>0.6542129328723593</v>
+        <v>0.6542129328723588</v>
       </c>
       <c r="AD74" s="188" t="n">
-        <v>558365.1154446254</v>
+        <v>558365.1154446251</v>
       </c>
       <c r="AE74" s="189" t="n">
-        <v>722963.0125383057</v>
+        <v>722963.012538305</v>
       </c>
       <c r="AF74" s="189" t="n">
-        <v>335712.0464231662</v>
+        <v>335712.0464231661</v>
       </c>
       <c r="AG74" s="189" t="n">
-        <v>296060.3965383623</v>
+        <v>296060.3965383621</v>
       </c>
       <c r="AH74" s="190" t="n">
-        <v>358082.3922811656</v>
+        <v>358082.3922811653</v>
       </c>
     </row>
     <row r="75" ht="15" customHeight="1" thickBot="1"/>
@@ -8260,49 +8260,49 @@
         </is>
       </c>
       <c r="C79" s="148" t="n">
-        <v>222.608217120298</v>
+        <v>222.6082171202978</v>
       </c>
       <c r="D79" s="149" t="n">
         <v>257.1762540061331</v>
       </c>
       <c r="E79" s="149" t="n">
-        <v>292.1642801895782</v>
+        <v>292.1642801895781</v>
       </c>
       <c r="F79" s="149" t="n">
-        <v>320.7007119048811</v>
+        <v>320.700711904881</v>
       </c>
       <c r="G79" s="150" t="n">
-        <v>342.1348723613771</v>
+        <v>342.1348723613769</v>
       </c>
       <c r="H79" s="148" t="n">
-        <v>41.00609317615557</v>
+        <v>41.00609317615554</v>
       </c>
       <c r="I79" s="149" t="n">
         <v>45.57324842173283</v>
       </c>
       <c r="J79" s="149" t="n">
-        <v>50.81005218525132</v>
+        <v>50.81005218525129</v>
       </c>
       <c r="K79" s="149" t="n">
-        <v>58.09169742555952</v>
+        <v>58.09169742555949</v>
       </c>
       <c r="L79" s="150" t="n">
-        <v>63.36045448144262</v>
+        <v>63.36045448144258</v>
       </c>
       <c r="M79" s="151" t="n">
-        <v>12127998.91668879</v>
+        <v>12127998.91668878</v>
       </c>
       <c r="N79" s="152" t="n">
         <v>13652829.57775516</v>
       </c>
       <c r="O79" s="152" t="n">
-        <v>15413843.69848081</v>
+        <v>15413843.6984808</v>
       </c>
       <c r="P79" s="152" t="n">
-        <v>17852598.59062992</v>
+        <v>17852598.59062991</v>
       </c>
       <c r="Q79" s="153" t="n">
-        <v>19810500.25376474</v>
+        <v>19810500.25376473</v>
       </c>
       <c r="S79" s="21" t="inlineStr">
         <is>
@@ -8310,49 +8310,49 @@
         </is>
       </c>
       <c r="T79" s="148" t="n">
-        <v>273.8342021396571</v>
+        <v>273.8342021396569</v>
       </c>
       <c r="U79" s="149" t="n">
-        <v>316.3569397214936</v>
+        <v>316.3569397214935</v>
       </c>
       <c r="V79" s="149" t="n">
-        <v>359.3963133723215</v>
+        <v>359.3963133723212</v>
       </c>
       <c r="W79" s="149" t="n">
-        <v>394.4994695440002</v>
+        <v>394.4994695439999</v>
       </c>
       <c r="X79" s="150" t="n">
-        <v>420.8659995089121</v>
+        <v>420.8659995089118</v>
       </c>
       <c r="Y79" s="148" t="n">
-        <v>50.87912095719047</v>
+        <v>50.87912095719044</v>
       </c>
       <c r="Z79" s="149" t="n">
-        <v>56.55011186824841</v>
+        <v>56.55011186824839</v>
       </c>
       <c r="AA79" s="149" t="n">
-        <v>63.05046950934313</v>
+        <v>63.0504695093431</v>
       </c>
       <c r="AB79" s="149" t="n">
-        <v>72.08076941270745</v>
+        <v>72.08076941270741</v>
       </c>
       <c r="AC79" s="150" t="n">
-        <v>78.61491562053239</v>
+        <v>78.61491562053234</v>
       </c>
       <c r="AD79" s="151" t="n">
-        <v>12127998.91668879</v>
+        <v>12127998.91668878</v>
       </c>
       <c r="AE79" s="152" t="n">
         <v>13652829.57775516</v>
       </c>
       <c r="AF79" s="152" t="n">
-        <v>15413843.69848081</v>
+        <v>15413843.6984808</v>
       </c>
       <c r="AG79" s="152" t="n">
-        <v>17852598.59062992</v>
+        <v>17852598.59062991</v>
       </c>
       <c r="AH79" s="153" t="n">
-        <v>19810500.25376474</v>
+        <v>19810500.25376473</v>
       </c>
     </row>
     <row r="80" ht="15" customHeight="1" thickBot="1">
@@ -8362,22 +8362,22 @@
         </is>
       </c>
       <c r="C80" s="155" t="n">
-        <v>304.4930117058337</v>
+        <v>304.4930117058336</v>
       </c>
       <c r="D80" s="156" t="n">
         <v>347.3800017063942</v>
       </c>
       <c r="E80" s="156" t="n">
-        <v>425.7087797595169</v>
+        <v>425.708779759517</v>
       </c>
       <c r="F80" s="156" t="n">
-        <v>464.0459906198863</v>
+        <v>464.0459906198862</v>
       </c>
       <c r="G80" s="157" t="n">
         <v>482.5323207386891</v>
       </c>
       <c r="H80" s="155" t="n">
-        <v>25.03083343969871</v>
+        <v>25.0308334396987</v>
       </c>
       <c r="I80" s="156" t="n">
         <v>23.10818145901083</v>
@@ -8386,22 +8386,22 @@
         <v>25.32668220472562</v>
       </c>
       <c r="K80" s="156" t="n">
-        <v>28.93376264150738</v>
+        <v>28.93376264150737</v>
       </c>
       <c r="L80" s="157" t="n">
         <v>31.86146664327443</v>
       </c>
       <c r="M80" s="158" t="n">
-        <v>6791360.615623762</v>
+        <v>6791360.61562376</v>
       </c>
       <c r="N80" s="159" t="n">
-        <v>6320138.304217423</v>
+        <v>6320138.304217422</v>
       </c>
       <c r="O80" s="159" t="n">
         <v>6980539.802886718</v>
       </c>
       <c r="P80" s="159" t="n">
-        <v>8030003.027625098</v>
+        <v>8030003.027625096</v>
       </c>
       <c r="Q80" s="160" t="n">
         <v>8924374.538327038</v>
@@ -8412,46 +8412,46 @@
         </is>
       </c>
       <c r="T80" s="155" t="n">
-        <v>362.2157197564746</v>
+        <v>362.2157197564745</v>
       </c>
       <c r="U80" s="156" t="n">
-        <v>413.2327919191989</v>
+        <v>413.2327919191988</v>
       </c>
       <c r="V80" s="156" t="n">
-        <v>506.4103481501664</v>
+        <v>506.4103481501666</v>
       </c>
       <c r="W80" s="156" t="n">
-        <v>552.0151400219083</v>
+        <v>552.0151400219082</v>
       </c>
       <c r="X80" s="157" t="n">
         <v>574.0059217877208</v>
       </c>
       <c r="Y80" s="155" t="n">
-        <v>26.17876930094959</v>
+        <v>26.17876930094958</v>
       </c>
       <c r="Z80" s="156" t="n">
-        <v>24.11815322259782</v>
+        <v>24.11815322259781</v>
       </c>
       <c r="AA80" s="156" t="n">
         <v>26.40923468263589</v>
       </c>
       <c r="AB80" s="156" t="n">
-        <v>30.18181526899115</v>
+        <v>30.18181526899114</v>
       </c>
       <c r="AC80" s="157" t="n">
         <v>33.2518642322725</v>
       </c>
       <c r="AD80" s="158" t="n">
-        <v>6791360.615623762</v>
+        <v>6791360.61562376</v>
       </c>
       <c r="AE80" s="159" t="n">
-        <v>6320138.304217423</v>
+        <v>6320138.304217422</v>
       </c>
       <c r="AF80" s="159" t="n">
         <v>6980539.802886718</v>
       </c>
       <c r="AG80" s="159" t="n">
-        <v>8030003.027625098</v>
+        <v>8030003.027625096</v>
       </c>
       <c r="AH80" s="160" t="n">
         <v>8924374.538327038</v>
@@ -8464,37 +8464,37 @@
         </is>
       </c>
       <c r="C81" s="161" t="n">
-        <v>246.393331561206</v>
+        <v>246.3933315612059</v>
       </c>
       <c r="D81" s="162" t="n">
         <v>280.199762762688</v>
       </c>
       <c r="E81" s="162" t="n">
-        <v>323.829273451949</v>
+        <v>323.8292734519489</v>
       </c>
       <c r="F81" s="162" t="n">
-        <v>354.6932050467335</v>
+        <v>354.6932050467333</v>
       </c>
       <c r="G81" s="163" t="n">
-        <v>376.1233387048964</v>
+        <v>376.1233387048962</v>
       </c>
       <c r="H81" s="161" t="n">
-        <v>33.36272908199894</v>
+        <v>33.36272908199891</v>
       </c>
       <c r="I81" s="162" t="n">
-        <v>34.85184381499515</v>
+        <v>34.85184381499514</v>
       </c>
       <c r="J81" s="162" t="n">
-        <v>38.67888896805883</v>
+        <v>38.67888896805881</v>
       </c>
       <c r="K81" s="162" t="n">
-        <v>44.25525416709755</v>
+        <v>44.25525416709752</v>
       </c>
       <c r="L81" s="163" t="n">
-        <v>48.47617910938313</v>
+        <v>48.47617910938311</v>
       </c>
       <c r="M81" s="164" t="n">
-        <v>18919359.53231256</v>
+        <v>18919359.53231255</v>
       </c>
       <c r="N81" s="165" t="n">
         <v>19972967.88197258</v>
@@ -8503,10 +8503,10 @@
         <v>22394383.50136752</v>
       </c>
       <c r="P81" s="165" t="n">
-        <v>25882601.61825502</v>
+        <v>25882601.618255</v>
       </c>
       <c r="Q81" s="166" t="n">
-        <v>28734874.79209178</v>
+        <v>28734874.79209177</v>
       </c>
       <c r="S81" s="42" t="inlineStr">
         <is>
@@ -8514,37 +8514,37 @@
         </is>
       </c>
       <c r="T81" s="161" t="n">
-        <v>300.1212136810968</v>
+        <v>300.1212136810967</v>
       </c>
       <c r="U81" s="162" t="n">
-        <v>341.7057148743657</v>
+        <v>341.7057148743656</v>
       </c>
       <c r="V81" s="162" t="n">
-        <v>395.1542797635252</v>
+        <v>395.154279763525</v>
       </c>
       <c r="W81" s="162" t="n">
-        <v>432.8157762279389</v>
+        <v>432.8157762279386</v>
       </c>
       <c r="X81" s="163" t="n">
-        <v>458.8891709779602</v>
+        <v>458.88917097796</v>
       </c>
       <c r="Y81" s="161" t="n">
-        <v>38.00660698813339</v>
+        <v>38.00660698813337</v>
       </c>
       <c r="Z81" s="162" t="n">
-        <v>39.6700003777169</v>
+        <v>39.67000037771689</v>
       </c>
       <c r="AA81" s="162" t="n">
-        <v>44.01496037850977</v>
+        <v>44.01496037850976</v>
       </c>
       <c r="AB81" s="162" t="n">
-        <v>50.38179374703351</v>
+        <v>50.38179374703348</v>
       </c>
       <c r="AC81" s="163" t="n">
-        <v>55.21887770736054</v>
+        <v>55.21887770736052</v>
       </c>
       <c r="AD81" s="164" t="n">
-        <v>18919359.53231256</v>
+        <v>18919359.53231255</v>
       </c>
       <c r="AE81" s="165" t="n">
         <v>19972967.88197258</v>
@@ -8553,10 +8553,10 @@
         <v>22394383.50136752</v>
       </c>
       <c r="AG81" s="165" t="n">
-        <v>25882601.61825502</v>
+        <v>25882601.618255</v>
       </c>
       <c r="AH81" s="166" t="n">
-        <v>28734874.79209178</v>
+        <v>28734874.79209177</v>
       </c>
     </row>
     <row r="82" ht="15" customHeight="1" thickBot="1">
@@ -8572,13 +8572,13 @@
         <v>628.4455885786257</v>
       </c>
       <c r="E82" s="156" t="n">
-        <v>729.1389169093915</v>
+        <v>729.1389169093916</v>
       </c>
       <c r="F82" s="156" t="n">
-        <v>804.129505084947</v>
+        <v>804.1295050849471</v>
       </c>
       <c r="G82" s="157" t="n">
-        <v>860.7376854395829</v>
+        <v>860.7376854395833</v>
       </c>
       <c r="H82" s="155" t="n">
         <v>45.79467044591771</v>
@@ -8593,7 +8593,7 @@
         <v>61.07759875567307</v>
       </c>
       <c r="L82" s="157" t="n">
-        <v>71.42090630252366</v>
+        <v>71.42090630252368</v>
       </c>
       <c r="M82" s="158" t="n">
         <v>194957.4907318928</v>
@@ -8608,7 +8608,7 @@
         <v>267884.9127093637</v>
       </c>
       <c r="Q82" s="160" t="n">
-        <v>317171.6480018383</v>
+        <v>317171.6480018384</v>
       </c>
       <c r="S82" s="32" t="inlineStr">
         <is>
@@ -8622,13 +8622,13 @@
         <v>642.7499251480982</v>
       </c>
       <c r="V82" s="156" t="n">
-        <v>745.7351802342118</v>
+        <v>745.735180234212</v>
       </c>
       <c r="W82" s="156" t="n">
-        <v>822.4326633777661</v>
+        <v>822.4326633777662</v>
       </c>
       <c r="X82" s="157" t="n">
-        <v>880.3293283348789</v>
+        <v>880.3293283348792</v>
       </c>
       <c r="Y82" s="155" t="n">
         <v>46.50651962670209</v>
@@ -8637,13 +8637,13 @@
         <v>46.97442313946731</v>
       </c>
       <c r="AA82" s="156" t="n">
-        <v>52.20468685416086</v>
+        <v>52.20468685416087</v>
       </c>
       <c r="AB82" s="156" t="n">
         <v>62.02261705465592</v>
       </c>
       <c r="AC82" s="157" t="n">
-        <v>72.52988838633281</v>
+        <v>72.52988838633283</v>
       </c>
       <c r="AD82" s="158" t="n">
         <v>194957.4907318928</v>
@@ -8658,7 +8658,7 @@
         <v>267884.9127093637</v>
       </c>
       <c r="AH82" s="160" t="n">
-        <v>317171.6480018383</v>
+        <v>317171.6480018384</v>
       </c>
     </row>
     <row r="83" ht="15" customHeight="1" thickTop="1">
@@ -8668,49 +8668,49 @@
         </is>
       </c>
       <c r="C83" s="161" t="n">
-        <v>247.7627764566513</v>
+        <v>247.7627764566512</v>
       </c>
       <c r="D83" s="162" t="n">
         <v>281.7396010690288</v>
       </c>
       <c r="E83" s="162" t="n">
-        <v>325.6164487905561</v>
+        <v>325.616448790556</v>
       </c>
       <c r="F83" s="162" t="n">
-        <v>356.7356820802004</v>
+        <v>356.7356820802002</v>
       </c>
       <c r="G83" s="163" t="n">
-        <v>378.4495602999133</v>
+        <v>378.4495602999132</v>
       </c>
       <c r="H83" s="161" t="n">
-        <v>33.45536318609319</v>
+        <v>33.45536318609317</v>
       </c>
       <c r="I83" s="162" t="n">
-        <v>34.93681830647735</v>
+        <v>34.93681830647734</v>
       </c>
       <c r="J83" s="162" t="n">
-        <v>38.77370387128838</v>
+        <v>38.77370387128836</v>
       </c>
       <c r="K83" s="162" t="n">
-        <v>44.38047164873012</v>
+        <v>44.38047164873009</v>
       </c>
       <c r="L83" s="163" t="n">
-        <v>48.64679891324703</v>
+        <v>48.64679891324701</v>
       </c>
       <c r="M83" s="164" t="n">
-        <v>19114317.02304445</v>
+        <v>19114317.02304444</v>
       </c>
       <c r="N83" s="165" t="n">
         <v>20171923.54249777</v>
       </c>
       <c r="O83" s="165" t="n">
-        <v>22617706.12749873</v>
+        <v>22617706.12749872</v>
       </c>
       <c r="P83" s="165" t="n">
-        <v>26150486.53096438</v>
+        <v>26150486.53096437</v>
       </c>
       <c r="Q83" s="166" t="n">
-        <v>29052046.44009362</v>
+        <v>29052046.44009361</v>
       </c>
       <c r="S83" s="42" t="inlineStr">
         <is>
@@ -8718,49 +8718,49 @@
         </is>
       </c>
       <c r="T83" s="161" t="n">
-        <v>301.5187731867451</v>
+        <v>301.5187731867449</v>
       </c>
       <c r="U83" s="162" t="n">
-        <v>343.2915584793586</v>
+        <v>343.2915584793585</v>
       </c>
       <c r="V83" s="162" t="n">
-        <v>396.9970665420536</v>
+        <v>396.9970665420535</v>
       </c>
       <c r="W83" s="162" t="n">
-        <v>434.9264529790294</v>
+        <v>434.9264529790292</v>
       </c>
       <c r="X83" s="163" t="n">
-        <v>461.3001418412259</v>
+        <v>461.3001418412258</v>
       </c>
       <c r="Y83" s="161" t="n">
-        <v>38.07758947509447</v>
+        <v>38.07758947509445</v>
       </c>
       <c r="Z83" s="162" t="n">
-        <v>39.7309347321952</v>
+        <v>39.73093473219519</v>
       </c>
       <c r="AA83" s="162" t="n">
-        <v>44.08324416866598</v>
+        <v>44.08324416866597</v>
       </c>
       <c r="AB83" s="162" t="n">
-        <v>50.47884731827362</v>
+        <v>50.47884731827359</v>
       </c>
       <c r="AC83" s="163" t="n">
-        <v>55.36313697871922</v>
+        <v>55.3631369787192</v>
       </c>
       <c r="AD83" s="164" t="n">
-        <v>19114317.02304445</v>
+        <v>19114317.02304444</v>
       </c>
       <c r="AE83" s="165" t="n">
         <v>20171923.54249777</v>
       </c>
       <c r="AF83" s="165" t="n">
-        <v>22617706.12749873</v>
+        <v>22617706.12749872</v>
       </c>
       <c r="AG83" s="165" t="n">
-        <v>26150486.53096438</v>
+        <v>26150486.53096437</v>
       </c>
       <c r="AH83" s="166" t="n">
-        <v>29052046.44009362</v>
+        <v>29052046.44009361</v>
       </c>
     </row>
     <row r="84" ht="15" customHeight="1" thickBot="1">
@@ -8770,49 +8770,49 @@
         </is>
       </c>
       <c r="C84" s="155" t="n">
-        <v>977.4180842620627</v>
+        <v>977.4180842620625</v>
       </c>
       <c r="D84" s="156" t="n">
         <v>1019.233029543745</v>
       </c>
       <c r="E84" s="156" t="n">
-        <v>898.5105926452326</v>
+        <v>898.5105926452322</v>
       </c>
       <c r="F84" s="156" t="n">
-        <v>939.7454315634831</v>
+        <v>939.7454315634824</v>
       </c>
       <c r="G84" s="157" t="n">
-        <v>982.1007605353432</v>
+        <v>982.1007605353428</v>
       </c>
       <c r="H84" s="155" t="n">
-        <v>855.1977867881255</v>
+        <v>855.1977867881253</v>
       </c>
       <c r="I84" s="156" t="n">
-        <v>897.2649103772727</v>
+        <v>897.2649103772724</v>
       </c>
       <c r="J84" s="156" t="n">
-        <v>791.665109557127</v>
+        <v>791.6651095571267</v>
       </c>
       <c r="K84" s="156" t="n">
-        <v>833.625404564693</v>
+        <v>833.6254045646924</v>
       </c>
       <c r="L84" s="157" t="n">
-        <v>879.054810250664</v>
+        <v>879.0548102506636</v>
       </c>
       <c r="M84" s="158" t="n">
-        <v>7879505.517718391</v>
+        <v>7879505.51771839</v>
       </c>
       <c r="N84" s="159" t="n">
-        <v>9264333.420513242</v>
+        <v>9264333.420513239</v>
       </c>
       <c r="O84" s="159" t="n">
-        <v>9210107.874456571</v>
+        <v>9210107.874456568</v>
       </c>
       <c r="P84" s="159" t="n">
-        <v>10915749.91958314</v>
+        <v>10915749.91958313</v>
       </c>
       <c r="Q84" s="160" t="n">
-        <v>13012027.24759935</v>
+        <v>13012027.24759934</v>
       </c>
       <c r="S84" s="32" t="inlineStr">
         <is>
@@ -8820,49 +8820,49 @@
         </is>
       </c>
       <c r="T84" s="155" t="n">
-        <v>637.8812783952496</v>
+        <v>637.8812783952495</v>
       </c>
       <c r="U84" s="156" t="n">
-        <v>665.1704918667241</v>
+        <v>665.1704918667239</v>
       </c>
       <c r="V84" s="156" t="n">
-        <v>586.384777115035</v>
+        <v>586.3847771150348</v>
       </c>
       <c r="W84" s="156" t="n">
-        <v>613.2954023501454</v>
+        <v>613.295402350145</v>
       </c>
       <c r="X84" s="157" t="n">
-        <v>640.937280300275</v>
+        <v>640.9372803002748</v>
       </c>
       <c r="Y84" s="155" t="n">
-        <v>560.6910690826734</v>
+        <v>560.6910690826733</v>
       </c>
       <c r="Z84" s="156" t="n">
-        <v>588.154818955014</v>
+        <v>588.1548189550138</v>
       </c>
       <c r="AA84" s="156" t="n">
-        <v>518.9200284044698</v>
+        <v>518.9200284044696</v>
       </c>
       <c r="AB84" s="156" t="n">
-        <v>546.3035144385175</v>
+        <v>546.3035144385171</v>
       </c>
       <c r="AC84" s="157" t="n">
-        <v>575.9051813143481</v>
+        <v>575.9051813143478</v>
       </c>
       <c r="AD84" s="158" t="n">
-        <v>7879505.517718391</v>
+        <v>7879505.51771839</v>
       </c>
       <c r="AE84" s="159" t="n">
-        <v>9264333.420513242</v>
+        <v>9264333.420513239</v>
       </c>
       <c r="AF84" s="159" t="n">
-        <v>9210107.874456571</v>
+        <v>9210107.874456568</v>
       </c>
       <c r="AG84" s="159" t="n">
-        <v>10915749.91958314</v>
+        <v>10915749.91958313</v>
       </c>
       <c r="AH84" s="160" t="n">
-        <v>13012027.24759935</v>
+        <v>13012027.24759934</v>
       </c>
     </row>
     <row r="85" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -8872,49 +8872,49 @@
         </is>
       </c>
       <c r="C85" s="179" t="n">
-        <v>316.7946763547364</v>
+        <v>316.7946763547362</v>
       </c>
       <c r="D85" s="180" t="n">
         <v>364.8190891421731</v>
       </c>
       <c r="E85" s="180" t="n">
-        <v>399.2870703808555</v>
+        <v>399.2870703808554</v>
       </c>
       <c r="F85" s="180" t="n">
-        <v>436.4811863999034</v>
+        <v>436.4811863999033</v>
       </c>
       <c r="G85" s="181" t="n">
-        <v>467.299963433506</v>
+        <v>467.2999634335058</v>
       </c>
       <c r="H85" s="179" t="n">
-        <v>46.49685589258148</v>
+        <v>46.49685589258146</v>
       </c>
       <c r="I85" s="180" t="n">
-        <v>50.08653092010205</v>
+        <v>50.08653092010203</v>
       </c>
       <c r="J85" s="180" t="n">
-        <v>53.49574282517765</v>
+        <v>53.49574282517763</v>
       </c>
       <c r="K85" s="180" t="n">
-        <v>61.53825193390818</v>
+        <v>61.53825193390816</v>
       </c>
       <c r="L85" s="181" t="n">
-        <v>68.73147775105375</v>
+        <v>68.7314777510537</v>
       </c>
       <c r="M85" s="182" t="n">
-        <v>26993822.54076284</v>
+        <v>26993822.54076283</v>
       </c>
       <c r="N85" s="183" t="n">
-        <v>29436256.96301101</v>
+        <v>29436256.963011</v>
       </c>
       <c r="O85" s="183" t="n">
-        <v>31827814.0019553</v>
+        <v>31827814.00195529</v>
       </c>
       <c r="P85" s="183" t="n">
-        <v>37066236.45054752</v>
+        <v>37066236.4505475</v>
       </c>
       <c r="Q85" s="184" t="n">
-        <v>42064073.68769296</v>
+        <v>42064073.68769294</v>
       </c>
       <c r="S85" s="51" t="inlineStr">
         <is>
@@ -8922,49 +8922,49 @@
         </is>
       </c>
       <c r="T85" s="185" t="n">
-        <v>356.3725511139157</v>
+        <v>356.3725511139155</v>
       </c>
       <c r="U85" s="186" t="n">
-        <v>404.9667550105227</v>
+        <v>404.9667550105225</v>
       </c>
       <c r="V85" s="186" t="n">
-        <v>437.9257208651933</v>
+        <v>437.9257208651932</v>
       </c>
       <c r="W85" s="186" t="n">
-        <v>475.667081834498</v>
+        <v>475.6670818344978</v>
       </c>
       <c r="X85" s="187" t="n">
-        <v>505.0910445654742</v>
+        <v>505.091044565474</v>
       </c>
       <c r="Y85" s="185" t="n">
-        <v>52.30990104324962</v>
+        <v>52.3099010432496</v>
       </c>
       <c r="Z85" s="186" t="n">
-        <v>56.2334972025556</v>
+        <v>56.23349720255558</v>
       </c>
       <c r="AA85" s="186" t="n">
-        <v>59.96008382574407</v>
+        <v>59.96008382574405</v>
       </c>
       <c r="AB85" s="186" t="n">
-        <v>68.89257046975366</v>
+        <v>68.89257046975364</v>
       </c>
       <c r="AC85" s="187" t="n">
-        <v>76.85063998951642</v>
+        <v>76.85063998951638</v>
       </c>
       <c r="AD85" s="188" t="n">
-        <v>26993822.54076284</v>
+        <v>26993822.54076283</v>
       </c>
       <c r="AE85" s="189" t="n">
-        <v>29436256.96301101</v>
+        <v>29436256.963011</v>
       </c>
       <c r="AF85" s="189" t="n">
-        <v>31827814.0019553</v>
+        <v>31827814.00195529</v>
       </c>
       <c r="AG85" s="189" t="n">
-        <v>37066236.45054752</v>
+        <v>37066236.4505475</v>
       </c>
       <c r="AH85" s="190" t="n">
-        <v>42064073.68769296</v>
+        <v>42064073.68769294</v>
       </c>
     </row>
     <row r="86" ht="15" customHeight="1" thickBot="1"/>
@@ -9284,7 +9284,7 @@
         <v>54481.36224969088</v>
       </c>
       <c r="D90" s="75" t="n">
-        <v>53087.44242549536</v>
+        <v>53087.44242549535</v>
       </c>
       <c r="E90" s="75" t="n">
         <v>52757.45443104524</v>
@@ -9460,7 +9460,7 @@
         <v>15294.37747392813</v>
       </c>
       <c r="V91" s="80" t="n">
-        <v>13784.35458198175</v>
+        <v>13784.35458198174</v>
       </c>
       <c r="W91" s="80" t="n">
         <v>14546.70795316665</v>
@@ -9527,7 +9527,7 @@
         <v>76785.19305873683</v>
       </c>
       <c r="D92" s="86" t="n">
-        <v>71281.17342086569</v>
+        <v>71281.17342086567</v>
       </c>
       <c r="E92" s="86" t="n">
         <v>69154.90765442021</v>
@@ -9695,7 +9695,7 @@
         <v>299.4663951096735</v>
       </c>
       <c r="W93" s="80" t="n">
-        <v>325.7226088384536</v>
+        <v>325.7226088384535</v>
       </c>
       <c r="X93" s="81" t="n">
         <v>360.2874944559221</v>
@@ -9759,7 +9759,7 @@
         <v>77147.65428610983</v>
       </c>
       <c r="D94" s="86" t="n">
-        <v>71597.75716994597</v>
+        <v>71597.75716994595</v>
       </c>
       <c r="E94" s="86" t="n">
         <v>69461.19034068499</v>
@@ -9991,7 +9991,7 @@
         <v>85209.20506421653</v>
       </c>
       <c r="D96" s="133" t="n">
-        <v>80687.27168917263</v>
+        <v>80687.2716891726</v>
       </c>
       <c r="E96" s="133" t="n">
         <v>79711.60691879326</v>
@@ -10044,7 +10044,7 @@
         <v>72688.08266062764</v>
       </c>
       <c r="V96" s="136" t="n">
-        <v>72678.56735857918</v>
+        <v>72678.56735857917</v>
       </c>
       <c r="W96" s="136" t="n">
         <v>77924.74582767999</v>
